--- a/hasil_aturan_asosiasi.xlsx
+++ b/hasil_aturan_asosiasi.xlsx
@@ -503,12 +503,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -551,7 +551,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Game Edukasi', 'Teknologi IoT', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS', 'Game Edukasi', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -599,12 +599,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -647,12 +647,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Game Edukasi', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -695,7 +695,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Data mining', 'Game Edukasi', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Game Edukasi', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -839,12 +839,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -887,12 +887,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -935,7 +935,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -983,7 +983,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Desain Grafis', 'Data mining'})</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining'})</t>
+          <t>frozenset({'Desain Grafis', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1127,7 +1127,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1223,12 +1223,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1271,7 +1271,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1367,12 +1367,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Game Edukasi', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1463,12 +1463,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1511,7 +1511,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1559,7 +1559,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1607,25 +1607,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="D25" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="E25" t="n">
         <v>0.14</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.7777777777777779</v>
       </c>
       <c r="G25" t="n">
         <v>1.234567901234568</v>
@@ -1637,43 +1637,43 @@
         <v>0.02660000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>1.38</v>
+        <v>1.665000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2405063291139241</v>
+        <v>0.2317073170731708</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2295081967213115</v>
+        <v>0.208955223880597</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2753623188405798</v>
+        <v>0.3993993993993997</v>
       </c>
       <c r="N25" t="n">
-        <v>0.462962962962963</v>
+        <v>0.5000000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="D26" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="E26" t="n">
         <v>0.14</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7777777777777779</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="G26" t="n">
         <v>1.234567901234568</v>
@@ -1685,25 +1685,25 @@
         <v>0.02660000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>1.665000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2317073170731708</v>
+        <v>0.2405063291139241</v>
       </c>
       <c r="L26" t="n">
-        <v>0.208955223880597</v>
+        <v>0.2295081967213115</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3993993993993997</v>
+        <v>0.2753623188405798</v>
       </c>
       <c r="N26" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.462962962962963</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1751,7 +1751,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1799,7 +1799,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1847,22 +1847,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="D30" t="n">
         <v>0.51</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="F30" t="n">
         <v>0.625</v>
@@ -1874,43 +1874,43 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0184</v>
+        <v>0.0276</v>
       </c>
       <c r="J30" t="n">
         <v>1.306666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>0.219047619047619</v>
+        <v>0.2421052631578947</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1754385964912281</v>
+        <v>0.25</v>
       </c>
       <c r="M30" t="n">
         <v>0.2346938775510204</v>
       </c>
       <c r="N30" t="n">
-        <v>0.4105392156862745</v>
+        <v>0.4595588235294118</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
       <c r="D31" t="n">
         <v>0.51</v>
       </c>
       <c r="E31" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="F31" t="n">
         <v>0.625</v>
@@ -1922,28 +1922,28 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0276</v>
+        <v>0.0184</v>
       </c>
       <c r="J31" t="n">
         <v>1.306666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2421052631578947</v>
+        <v>0.219047619047619</v>
       </c>
       <c r="L31" t="n">
-        <v>0.25</v>
+        <v>0.1754385964912281</v>
       </c>
       <c r="M31" t="n">
         <v>0.2346938775510204</v>
       </c>
       <c r="N31" t="n">
-        <v>0.4595588235294118</v>
+        <v>0.4105392156862745</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Game Edukasi', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1991,7 +1991,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2039,22 +2039,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="D34" t="n">
         <v>0.55</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="F34" t="n">
         <v>0.6666666666666667</v>
@@ -2066,43 +2066,43 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0175</v>
+        <v>0.02450000000000001</v>
       </c>
       <c r="J34" t="n">
         <v>1.35</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2058823529411765</v>
+        <v>0.2215189873417722</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="M34" t="n">
         <v>0.2592592592592594</v>
       </c>
       <c r="N34" t="n">
-        <v>0.4242424242424243</v>
+        <v>0.4606060606060607</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="D35" t="n">
         <v>0.55</v>
       </c>
       <c r="E35" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="F35" t="n">
         <v>0.6666666666666667</v>
@@ -2114,28 +2114,28 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.02450000000000001</v>
+        <v>0.0175</v>
       </c>
       <c r="J35" t="n">
         <v>1.35</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2215189873417722</v>
+        <v>0.2058823529411765</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M35" t="n">
         <v>0.2592592592592594</v>
       </c>
       <c r="N35" t="n">
-        <v>0.4606060606060607</v>
+        <v>0.4242424242424243</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Desain Grafis', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2327,7 +2327,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2375,12 +2375,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2423,12 +2423,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2471,7 +2471,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Game Edukasi', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2567,12 +2567,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Game Edukasi', 'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2615,22 +2615,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="D46" t="n">
         <v>0.57</v>
       </c>
       <c r="E46" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="F46" t="n">
         <v>0.6666666666666667</v>
@@ -2642,43 +2642,43 @@
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0.02320000000000003</v>
+        <v>0.01450000000000001</v>
       </c>
       <c r="J46" t="n">
         <v>1.29</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1907894736842107</v>
+        <v>0.1705882352941178</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2461538461538462</v>
+        <v>0.1612903225806452</v>
       </c>
       <c r="M46" t="n">
         <v>0.2248062015503879</v>
       </c>
       <c r="N46" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4210526315789474</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="D47" t="n">
         <v>0.57</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="F47" t="n">
         <v>0.6666666666666667</v>
@@ -2690,22 +2690,22 @@
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0.01450000000000001</v>
+        <v>0.02320000000000003</v>
       </c>
       <c r="J47" t="n">
         <v>1.29</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1705882352941178</v>
+        <v>0.1907894736842107</v>
       </c>
       <c r="L47" t="n">
-        <v>0.1612903225806452</v>
+        <v>0.2461538461538462</v>
       </c>
       <c r="M47" t="n">
         <v>0.2248062015503879</v>
       </c>
       <c r="N47" t="n">
-        <v>0.4210526315789474</v>
+        <v>0.4736842105263158</v>
       </c>
     </row>
     <row r="48">
@@ -2759,12 +2759,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -2807,12 +2807,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -2855,7 +2855,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2903,7 +2903,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2951,7 +2951,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2960,13 +2960,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="D53" t="n">
         <v>0.62</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="F53" t="n">
         <v>0.7142857142857143</v>
@@ -2978,28 +2978,28 @@
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0132</v>
+        <v>0.01980000000000001</v>
       </c>
       <c r="J53" t="n">
         <v>1.33</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1534883720930233</v>
+        <v>0.1670886075949368</v>
       </c>
       <c r="L53" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.2205882352941177</v>
       </c>
       <c r="M53" t="n">
         <v>0.2481203007518797</v>
       </c>
       <c r="N53" t="n">
-        <v>0.4377880184331797</v>
+        <v>0.478110599078341</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining', 'Pemrograman CMS', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3008,13 +3008,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.21</v>
+        <v>0.14</v>
       </c>
       <c r="D54" t="n">
         <v>0.62</v>
       </c>
       <c r="E54" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="F54" t="n">
         <v>0.7142857142857143</v>
@@ -3026,28 +3026,28 @@
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.01980000000000001</v>
+        <v>0.0132</v>
       </c>
       <c r="J54" t="n">
         <v>1.33</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1670886075949368</v>
+        <v>0.1534883720930233</v>
       </c>
       <c r="L54" t="n">
-        <v>0.2205882352941177</v>
+        <v>0.1515151515151515</v>
       </c>
       <c r="M54" t="n">
         <v>0.2481203007518797</v>
       </c>
       <c r="N54" t="n">
-        <v>0.478110599078341</v>
+        <v>0.4377880184331797</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="D55" t="n">
         <v>0.87</v>
       </c>
       <c r="E55" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
@@ -3074,7 +3074,7 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>0.03120000000000001</v>
+        <v>0.0156</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3082,22 +3082,22 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0.1710526315789474</v>
+        <v>0.1477272727272728</v>
       </c>
       <c r="L55" t="n">
-        <v>0.2758620689655173</v>
+        <v>0.1379310344827586</v>
       </c>
       <c r="M55" t="n">
         <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>0.6379310344827587</v>
+        <v>0.5689655172413793</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3147,7 +3147,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3156,13 +3156,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="D57" t="n">
         <v>0.87</v>
       </c>
       <c r="E57" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -3174,7 +3174,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>0.02729999999999999</v>
+        <v>0.02080000000000001</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3182,22 +3182,22 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0.1645569620253164</v>
+        <v>0.1547619047619049</v>
       </c>
       <c r="L57" t="n">
-        <v>0.2413793103448275</v>
+        <v>0.1839080459770115</v>
       </c>
       <c r="M57" t="n">
         <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.5919540229885057</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Data mining'})</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3247,7 +3247,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Game Edukasi', 'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3256,13 +3256,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="D59" t="n">
         <v>0.87</v>
       </c>
       <c r="E59" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
@@ -3274,7 +3274,7 @@
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.02080000000000001</v>
+        <v>0.01949999999999999</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3282,22 +3282,22 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>0.1547619047619049</v>
+        <v>0.1529411764705882</v>
       </c>
       <c r="L59" t="n">
-        <v>0.1839080459770115</v>
+        <v>0.1724137931034483</v>
       </c>
       <c r="M59" t="n">
         <v>1</v>
       </c>
       <c r="N59" t="n">
-        <v>0.5919540229885057</v>
+        <v>0.5862068965517241</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3306,13 +3306,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="D60" t="n">
         <v>0.87</v>
       </c>
       <c r="E60" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
@@ -3324,7 +3324,7 @@
         <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>0.01949999999999999</v>
+        <v>0.02729999999999999</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3332,22 +3332,22 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0.1529411764705882</v>
+        <v>0.1645569620253164</v>
       </c>
       <c r="L60" t="n">
-        <v>0.1724137931034483</v>
+        <v>0.2413793103448275</v>
       </c>
       <c r="M60" t="n">
         <v>1</v>
       </c>
       <c r="N60" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.6206896551724138</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3356,13 +3356,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="D61" t="n">
         <v>0.87</v>
       </c>
       <c r="E61" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="F61" t="n">
         <v>1</v>
@@ -3374,7 +3374,7 @@
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0.02080000000000001</v>
+        <v>0.03120000000000001</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3382,22 +3382,22 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0.1547619047619049</v>
+        <v>0.1710526315789474</v>
       </c>
       <c r="L61" t="n">
-        <v>0.1839080459770115</v>
+        <v>0.2758620689655173</v>
       </c>
       <c r="M61" t="n">
         <v>1</v>
       </c>
       <c r="N61" t="n">
-        <v>0.5919540229885057</v>
+        <v>0.6379310344827587</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="D62" t="n">
         <v>0.87</v>
       </c>
       <c r="E62" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
@@ -3424,7 +3424,7 @@
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0156</v>
+        <v>0.02080000000000001</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3432,16 +3432,16 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>0.1477272727272728</v>
+        <v>0.1547619047619049</v>
       </c>
       <c r="L62" t="n">
-        <v>0.1379310344827586</v>
+        <v>0.1839080459770115</v>
       </c>
       <c r="M62" t="n">
         <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>0.5689655172413793</v>
+        <v>0.5919540229885057</v>
       </c>
     </row>
     <row r="63">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -3543,12 +3543,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -3591,12 +3591,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -3639,12 +3639,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -3735,7 +3735,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3783,7 +3783,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3831,7 +3831,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3879,12 +3879,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Data mining'})</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -4023,7 +4023,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4071,25 +4071,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Desain Grafis', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.36</v>
+        <v>0.18</v>
       </c>
       <c r="D76" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="E76" t="n">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="F76" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G76" t="n">
         <v>1.111111111111111</v>
@@ -4098,28 +4098,28 @@
         <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>0.02199999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="J76" t="n">
-        <v>1.157142857142857</v>
+        <v>1.2</v>
       </c>
       <c r="K76" t="n">
-        <v>0.1562499999999999</v>
+        <v>0.1219512195121951</v>
       </c>
       <c r="L76" t="n">
-        <v>0.3188405797101449</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="M76" t="n">
-        <v>0.1358024691358025</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="N76" t="n">
-        <v>0.5055555555555555</v>
+        <v>0.4333333333333333</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Realitas Virtual', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4128,13 +4128,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="D77" t="n">
         <v>0.6</v>
       </c>
       <c r="E77" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="F77" t="n">
         <v>0.6666666666666666</v>
@@ -4146,46 +4146,46 @@
         <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>0.012</v>
+        <v>0.01799999999999999</v>
       </c>
       <c r="J77" t="n">
         <v>1.2</v>
       </c>
       <c r="K77" t="n">
-        <v>0.1219512195121951</v>
+        <v>0.1369863013698629</v>
       </c>
       <c r="L77" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="M77" t="n">
         <v>0.1666666666666666</v>
       </c>
       <c r="N77" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.4833333333333333</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Realitas Virtual'})</t>
+          <t>frozenset({'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="D78" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="E78" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="F78" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="G78" t="n">
         <v>1.111111111111111</v>
@@ -4194,28 +4194,28 @@
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.01799999999999999</v>
+        <v>0.02199999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>1.2</v>
+        <v>1.157142857142857</v>
       </c>
       <c r="K78" t="n">
-        <v>0.1369863013698629</v>
+        <v>0.1562499999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.3188405797101449</v>
       </c>
       <c r="M78" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.1358024691358025</v>
       </c>
       <c r="N78" t="n">
-        <v>0.4833333333333333</v>
+        <v>0.5055555555555555</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4263,7 +4263,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4311,7 +4311,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4359,12 +4359,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -4407,12 +4407,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -4503,12 +4503,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -4551,12 +4551,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -4599,7 +4599,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4695,7 +4695,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4791,7 +4791,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4839,25 +4839,25 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>frozenset({'Data mining'})</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
-        </is>
-      </c>
       <c r="C92" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D92" t="n">
         <v>0.64</v>
-      </c>
-      <c r="D92" t="n">
-        <v>0.65</v>
       </c>
       <c r="E92" t="n">
         <v>0.45</v>
       </c>
       <c r="F92" t="n">
-        <v>0.703125</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="G92" t="n">
         <v>1.081730769230769</v>
@@ -4869,16 +4869,16 @@
         <v>0.03399999999999997</v>
       </c>
       <c r="J92" t="n">
-        <v>1.178947368421053</v>
+        <v>1.17</v>
       </c>
       <c r="K92" t="n">
-        <v>0.2098765432098764</v>
+        <v>0.2158730158730157</v>
       </c>
       <c r="L92" t="n">
         <v>0.5357142857142857</v>
       </c>
       <c r="M92" t="n">
-        <v>0.1517857142857142</v>
+        <v>0.1452991452991452</v>
       </c>
       <c r="N92" t="n">
         <v>0.6977163461538461</v>
@@ -4887,25 +4887,25 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>frozenset({'Data mining'})</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>frozenset({'Data mining'})</t>
-        </is>
-      </c>
       <c r="C93" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D93" t="n">
         <v>0.65</v>
-      </c>
-      <c r="D93" t="n">
-        <v>0.64</v>
       </c>
       <c r="E93" t="n">
         <v>0.45</v>
       </c>
       <c r="F93" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.703125</v>
       </c>
       <c r="G93" t="n">
         <v>1.081730769230769</v>
@@ -4917,16 +4917,16 @@
         <v>0.03399999999999997</v>
       </c>
       <c r="J93" t="n">
-        <v>1.17</v>
+        <v>1.178947368421053</v>
       </c>
       <c r="K93" t="n">
-        <v>0.2158730158730157</v>
+        <v>0.2098765432098764</v>
       </c>
       <c r="L93" t="n">
         <v>0.5357142857142857</v>
       </c>
       <c r="M93" t="n">
-        <v>0.1452991452991452</v>
+        <v>0.1517857142857142</v>
       </c>
       <c r="N93" t="n">
         <v>0.6977163461538461</v>
@@ -4935,7 +4935,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4983,7 +4983,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Game Edukasi', 'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5175,7 +5175,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Game Edukasi', 'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5223,7 +5223,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -5319,7 +5319,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -5463,7 +5463,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5472,13 +5472,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0.16</v>
+        <v>0.45</v>
       </c>
       <c r="D105" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E105" t="n">
-        <v>0.16</v>
+        <v>0.45</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
@@ -5490,7 +5490,7 @@
         <v>1</v>
       </c>
       <c r="I105" t="n">
-        <v>0.009599999999999997</v>
+        <v>0.02700000000000002</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -5498,22 +5498,22 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>0.07142857142857141</v>
+        <v>0.1090909090909092</v>
       </c>
       <c r="L105" t="n">
-        <v>0.1702127659574468</v>
+        <v>0.4787234042553192</v>
       </c>
       <c r="M105" t="n">
         <v>1</v>
       </c>
       <c r="N105" t="n">
-        <v>0.5851063829787234</v>
+        <v>0.7393617021276596</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Desain Grafis', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5522,13 +5522,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.36</v>
+        <v>0.13</v>
       </c>
       <c r="D106" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E106" t="n">
-        <v>0.36</v>
+        <v>0.13</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
@@ -5540,7 +5540,7 @@
         <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>0.02160000000000001</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -5548,22 +5548,22 @@
         </is>
       </c>
       <c r="K106" t="n">
-        <v>0.09375000000000004</v>
+        <v>0.06896551724137932</v>
       </c>
       <c r="L106" t="n">
-        <v>0.3829787234042554</v>
+        <v>0.1382978723404256</v>
       </c>
       <c r="M106" t="n">
         <v>1</v>
       </c>
       <c r="N106" t="n">
-        <v>0.6914893617021276</v>
+        <v>0.5691489361702128</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5572,13 +5572,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="D107" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E107" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="F107" t="n">
         <v>1</v>
@@ -5590,7 +5590,7 @@
         <v>1</v>
       </c>
       <c r="I107" t="n">
-        <v>0.009599999999999997</v>
+        <v>0.0156</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -5598,22 +5598,22 @@
         </is>
       </c>
       <c r="K107" t="n">
-        <v>0.07142857142857141</v>
+        <v>0.08108108108108109</v>
       </c>
       <c r="L107" t="n">
-        <v>0.1702127659574468</v>
+        <v>0.2765957446808511</v>
       </c>
       <c r="M107" t="n">
         <v>1</v>
       </c>
       <c r="N107" t="n">
-        <v>0.5851063829787234</v>
+        <v>0.6382978723404256</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining', 'Game Edukasi'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5622,13 +5622,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0.13</v>
+        <v>0.33</v>
       </c>
       <c r="D108" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E108" t="n">
-        <v>0.13</v>
+        <v>0.33</v>
       </c>
       <c r="F108" t="n">
         <v>1</v>
@@ -5640,7 +5640,7 @@
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.01980000000000004</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -5648,22 +5648,22 @@
         </is>
       </c>
       <c r="K108" t="n">
-        <v>0.06896551724137932</v>
+        <v>0.08955223880597034</v>
       </c>
       <c r="L108" t="n">
-        <v>0.1382978723404256</v>
+        <v>0.3510638297872341</v>
       </c>
       <c r="M108" t="n">
         <v>1</v>
       </c>
       <c r="N108" t="n">
-        <v>0.5691489361702128</v>
+        <v>0.6755319148936171</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Desain Grafis', 'Data mining', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5672,13 +5672,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="D109" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E109" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F109" t="n">
         <v>1</v>
@@ -5690,7 +5690,7 @@
         <v>1</v>
       </c>
       <c r="I109" t="n">
-        <v>0.007200000000000012</v>
+        <v>0.006600000000000009</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -5698,22 +5698,22 @@
         </is>
       </c>
       <c r="K109" t="n">
-        <v>0.0681818181818183</v>
+        <v>0.06741573033707873</v>
       </c>
       <c r="L109" t="n">
-        <v>0.1276595744680851</v>
+        <v>0.1170212765957447</v>
       </c>
       <c r="M109" t="n">
         <v>1</v>
       </c>
       <c r="N109" t="n">
-        <v>0.5638297872340425</v>
+        <v>0.5585106382978724</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5763,7 +5763,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Realitas Virtual', 'Desain Grafis', 'Data mining'})</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5772,13 +5772,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="D111" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E111" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="F111" t="n">
         <v>1</v>
@@ -5790,7 +5790,7 @@
         <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>0.006600000000000009</v>
+        <v>0.007200000000000012</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="K111" t="n">
-        <v>0.06741573033707873</v>
+        <v>0.0681818181818183</v>
       </c>
       <c r="L111" t="n">
-        <v>0.1170212765957447</v>
+        <v>0.1276595744680851</v>
       </c>
       <c r="M111" t="n">
         <v>1</v>
       </c>
       <c r="N111" t="n">
-        <v>0.5585106382978724</v>
+        <v>0.5638297872340425</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="D112" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E112" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
@@ -5840,7 +5840,7 @@
         <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>0.01320000000000002</v>
+        <v>0.01440000000000002</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -5848,22 +5848,22 @@
         </is>
       </c>
       <c r="K112" t="n">
-        <v>0.07692307692307702</v>
+        <v>0.07894736842105277</v>
       </c>
       <c r="L112" t="n">
-        <v>0.2340425531914894</v>
+        <v>0.2553191489361702</v>
       </c>
       <c r="M112" t="n">
         <v>1</v>
       </c>
       <c r="N112" t="n">
-        <v>0.6170212765957447</v>
+        <v>0.6276595744680851</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5872,13 +5872,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="D113" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E113" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="F113" t="n">
         <v>1</v>
@@ -5890,7 +5890,7 @@
         <v>1</v>
       </c>
       <c r="I113" t="n">
-        <v>0.01440000000000002</v>
+        <v>0.009000000000000008</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -5898,22 +5898,22 @@
         </is>
       </c>
       <c r="K113" t="n">
-        <v>0.07894736842105277</v>
+        <v>0.0705882352941177</v>
       </c>
       <c r="L113" t="n">
-        <v>0.2553191489361702</v>
+        <v>0.1595744680851064</v>
       </c>
       <c r="M113" t="n">
         <v>1</v>
       </c>
       <c r="N113" t="n">
-        <v>0.6276595744680851</v>
+        <v>0.5797872340425532</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5922,13 +5922,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="D114" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E114" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="F114" t="n">
         <v>1</v>
@@ -5940,7 +5940,7 @@
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>0.006600000000000009</v>
+        <v>0.02400000000000002</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -5948,22 +5948,22 @@
         </is>
       </c>
       <c r="K114" t="n">
-        <v>0.06741573033707873</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="L114" t="n">
-        <v>0.1170212765957447</v>
+        <v>0.4255319148936171</v>
       </c>
       <c r="M114" t="n">
         <v>1</v>
       </c>
       <c r="N114" t="n">
-        <v>0.5585106382978724</v>
+        <v>0.7127659574468086</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="D115" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E115" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="F115" t="n">
         <v>1</v>
@@ -5990,7 +5990,7 @@
         <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>0.009000000000000008</v>
+        <v>0.006600000000000009</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -5998,22 +5998,22 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>0.0705882352941177</v>
+        <v>0.06741573033707873</v>
       </c>
       <c r="L115" t="n">
-        <v>0.1595744680851064</v>
+        <v>0.1170212765957447</v>
       </c>
       <c r="M115" t="n">
         <v>1</v>
       </c>
       <c r="N115" t="n">
-        <v>0.5797872340425532</v>
+        <v>0.5585106382978724</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Desain Grafis', 'Data mining'})</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6022,13 +6022,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="D116" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E116" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="F116" t="n">
         <v>1</v>
@@ -6040,7 +6040,7 @@
         <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>0.008400000000000019</v>
+        <v>0.009599999999999997</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -6048,22 +6048,22 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>0.06976744186046527</v>
+        <v>0.07142857142857141</v>
       </c>
       <c r="L116" t="n">
-        <v>0.148936170212766</v>
+        <v>0.1702127659574468</v>
       </c>
       <c r="M116" t="n">
         <v>1</v>
       </c>
       <c r="N116" t="n">
-        <v>0.574468085106383</v>
+        <v>0.5851063829787234</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6072,13 +6072,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="D117" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E117" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="F117" t="n">
         <v>1</v>
@@ -6090,7 +6090,7 @@
         <v>1</v>
       </c>
       <c r="I117" t="n">
-        <v>0.02400000000000002</v>
+        <v>0.02160000000000001</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -6098,22 +6098,22 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>0.1000000000000001</v>
+        <v>0.09375000000000004</v>
       </c>
       <c r="L117" t="n">
-        <v>0.4255319148936171</v>
+        <v>0.3829787234042554</v>
       </c>
       <c r="M117" t="n">
         <v>1</v>
       </c>
       <c r="N117" t="n">
-        <v>0.7127659574468086</v>
+        <v>0.6914893617021276</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6122,13 +6122,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>0.45</v>
+        <v>0.22</v>
       </c>
       <c r="D118" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E118" t="n">
-        <v>0.45</v>
+        <v>0.22</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
@@ -6140,7 +6140,7 @@
         <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.02700000000000002</v>
+        <v>0.01320000000000002</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -6148,22 +6148,22 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>0.1090909090909092</v>
+        <v>0.07692307692307702</v>
       </c>
       <c r="L118" t="n">
-        <v>0.4787234042553192</v>
+        <v>0.2340425531914894</v>
       </c>
       <c r="M118" t="n">
         <v>1</v>
       </c>
       <c r="N118" t="n">
-        <v>0.7393617021276596</v>
+        <v>0.6170212765957447</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining', 'Game Edukasi', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6172,13 +6172,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
       <c r="D119" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E119" t="n">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -6190,7 +6190,7 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0156</v>
+        <v>0.006000000000000005</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -6198,22 +6198,22 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>0.08108108108108109</v>
+        <v>0.06666666666666672</v>
       </c>
       <c r="L119" t="n">
-        <v>0.2765957446808511</v>
+        <v>0.1063829787234043</v>
       </c>
       <c r="M119" t="n">
         <v>1</v>
       </c>
       <c r="N119" t="n">
-        <v>0.6382978723404256</v>
+        <v>0.5531914893617021</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Informasi Pendidikan'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6222,13 +6222,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="D120" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E120" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="F120" t="n">
         <v>1</v>
@@ -6240,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>0.006000000000000005</v>
+        <v>0.008400000000000019</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -6248,22 +6248,22 @@
         </is>
       </c>
       <c r="K120" t="n">
-        <v>0.06666666666666672</v>
+        <v>0.06976744186046527</v>
       </c>
       <c r="L120" t="n">
-        <v>0.1063829787234043</v>
+        <v>0.148936170212766</v>
       </c>
       <c r="M120" t="n">
         <v>1</v>
       </c>
       <c r="N120" t="n">
-        <v>0.5531914893617021</v>
+        <v>0.574468085106383</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6272,13 +6272,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>0.33</v>
+        <v>0.16</v>
       </c>
       <c r="D121" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E121" t="n">
-        <v>0.33</v>
+        <v>0.16</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
@@ -6290,7 +6290,7 @@
         <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>0.01980000000000004</v>
+        <v>0.009599999999999997</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -6298,22 +6298,22 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>0.08955223880597034</v>
+        <v>0.07142857142857141</v>
       </c>
       <c r="L121" t="n">
-        <v>0.3510638297872341</v>
+        <v>0.1702127659574468</v>
       </c>
       <c r="M121" t="n">
         <v>1</v>
       </c>
       <c r="N121" t="n">
-        <v>0.6755319148936171</v>
+        <v>0.5851063829787234</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Teknologi IoT', 'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6322,13 +6322,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="D122" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E122" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="F122" t="n">
         <v>1</v>
@@ -6340,7 +6340,7 @@
         <v>1</v>
       </c>
       <c r="I122" t="n">
-        <v>0.006000000000000005</v>
+        <v>0.01140000000000002</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -6348,22 +6348,22 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>0.06666666666666672</v>
+        <v>0.07407407407407421</v>
       </c>
       <c r="L122" t="n">
-        <v>0.1063829787234043</v>
+        <v>0.2021276595744681</v>
       </c>
       <c r="M122" t="n">
         <v>1</v>
       </c>
       <c r="N122" t="n">
-        <v>0.5531914893617021</v>
+        <v>0.601063829787234</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Sistem Informasi Pendidikan'})</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6372,13 +6372,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="D123" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E123" t="n">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -6390,7 +6390,7 @@
         <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>0.01140000000000002</v>
+        <v>0.006000000000000005</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -6398,22 +6398,22 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>0.07407407407407421</v>
+        <v>0.06666666666666672</v>
       </c>
       <c r="L123" t="n">
-        <v>0.2021276595744681</v>
+        <v>0.1063829787234043</v>
       </c>
       <c r="M123" t="n">
         <v>1</v>
       </c>
       <c r="N123" t="n">
-        <v>0.601063829787234</v>
+        <v>0.5531914893617021</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -6653,7 +6653,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -6749,7 +6749,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Teknologi IoT', 'Pemrograman CMS', 'Data mining', 'Game Edukasi', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6758,13 +6758,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0.21</v>
+        <v>0.14</v>
       </c>
       <c r="D131" t="n">
         <v>0.68</v>
       </c>
       <c r="E131" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="F131" t="n">
         <v>0.7142857142857143</v>
@@ -6776,46 +6776,46 @@
         <v>1</v>
       </c>
       <c r="I131" t="n">
-        <v>0.007199999999999984</v>
+        <v>0.004799999999999985</v>
       </c>
       <c r="J131" t="n">
         <v>1.12</v>
       </c>
       <c r="K131" t="n">
-        <v>0.06075949367088595</v>
+        <v>0.05581395348837191</v>
       </c>
       <c r="L131" t="n">
-        <v>0.2027027027027027</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="M131" t="n">
         <v>0.1071428571428571</v>
       </c>
       <c r="N131" t="n">
-        <v>0.467436974789916</v>
+        <v>0.430672268907563</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
           <t>frozenset({'Pengolahan Citra Digital'})</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
-        </is>
-      </c>
       <c r="C132" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D132" t="n">
         <v>0.68</v>
       </c>
-      <c r="D132" t="n">
-        <v>0.63</v>
-      </c>
       <c r="E132" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="F132" t="n">
-        <v>0.6617647058823529</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="G132" t="n">
         <v>1.050420168067227</v>
@@ -6824,28 +6824,28 @@
         <v>1</v>
       </c>
       <c r="I132" t="n">
-        <v>0.02159999999999995</v>
+        <v>0.004799999999999985</v>
       </c>
       <c r="J132" t="n">
-        <v>1.093913043478261</v>
+        <v>1.12</v>
       </c>
       <c r="K132" t="n">
-        <v>0.1499999999999997</v>
+        <v>0.05581395348837191</v>
       </c>
       <c r="L132" t="n">
-        <v>0.5232558139534883</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="M132" t="n">
-        <v>0.08585055643879166</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="N132" t="n">
-        <v>0.6880252100840336</v>
+        <v>0.430672268907563</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Game Edukasi', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6854,13 +6854,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="D133" t="n">
         <v>0.68</v>
       </c>
       <c r="E133" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="F133" t="n">
         <v>0.7142857142857143</v>
@@ -6872,28 +6872,28 @@
         <v>1</v>
       </c>
       <c r="I133" t="n">
-        <v>0.004799999999999985</v>
+        <v>0.007199999999999984</v>
       </c>
       <c r="J133" t="n">
         <v>1.12</v>
       </c>
       <c r="K133" t="n">
-        <v>0.05581395348837191</v>
+        <v>0.06075949367088595</v>
       </c>
       <c r="L133" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.2027027027027027</v>
       </c>
       <c r="M133" t="n">
         <v>0.1071428571428571</v>
       </c>
       <c r="N133" t="n">
-        <v>0.430672268907563</v>
+        <v>0.467436974789916</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6902,13 +6902,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0.14</v>
+        <v>0.63</v>
       </c>
       <c r="D134" t="n">
         <v>0.68</v>
       </c>
       <c r="E134" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="F134" t="n">
         <v>0.7142857142857143</v>
@@ -6920,46 +6920,46 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.004799999999999985</v>
+        <v>0.02159999999999995</v>
       </c>
       <c r="J134" t="n">
         <v>1.12</v>
       </c>
       <c r="K134" t="n">
-        <v>0.05581395348837191</v>
+        <v>0.1297297297297294</v>
       </c>
       <c r="L134" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.5232558139534883</v>
       </c>
       <c r="M134" t="n">
         <v>0.1071428571428571</v>
       </c>
       <c r="N134" t="n">
-        <v>0.430672268907563</v>
+        <v>0.6880252100840336</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>0.21</v>
+        <v>0.68</v>
       </c>
       <c r="D135" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="E135" t="n">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="F135" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6617647058823529</v>
       </c>
       <c r="G135" t="n">
         <v>1.050420168067227</v>
@@ -6968,28 +6968,28 @@
         <v>1</v>
       </c>
       <c r="I135" t="n">
-        <v>0.007199999999999984</v>
+        <v>0.02159999999999995</v>
       </c>
       <c r="J135" t="n">
-        <v>1.12</v>
+        <v>1.093913043478261</v>
       </c>
       <c r="K135" t="n">
-        <v>0.06075949367088595</v>
+        <v>0.1499999999999997</v>
       </c>
       <c r="L135" t="n">
-        <v>0.2027027027027027</v>
+        <v>0.5232558139534883</v>
       </c>
       <c r="M135" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.08585055643879166</v>
       </c>
       <c r="N135" t="n">
-        <v>0.467436974789916</v>
+        <v>0.6880252100840336</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6998,13 +6998,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0.63</v>
+        <v>0.21</v>
       </c>
       <c r="D136" t="n">
         <v>0.68</v>
       </c>
       <c r="E136" t="n">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="F136" t="n">
         <v>0.7142857142857143</v>
@@ -7016,22 +7016,22 @@
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>0.02159999999999995</v>
+        <v>0.007199999999999984</v>
       </c>
       <c r="J136" t="n">
         <v>1.12</v>
       </c>
       <c r="K136" t="n">
-        <v>0.1297297297297294</v>
+        <v>0.06075949367088595</v>
       </c>
       <c r="L136" t="n">
-        <v>0.5232558139534883</v>
+        <v>0.2027027027027027</v>
       </c>
       <c r="M136" t="n">
         <v>0.1071428571428571</v>
       </c>
       <c r="N136" t="n">
-        <v>0.6880252100840336</v>
+        <v>0.467436974789916</v>
       </c>
     </row>
     <row r="137">
@@ -7133,7 +7133,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7181,7 +7181,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Teknologi IoT', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Desain Grafis', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7229,7 +7229,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7277,25 +7277,25 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C142" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D142" t="n">
         <v>0.55</v>
-      </c>
-      <c r="D142" t="n">
-        <v>0.9399999999999999</v>
       </c>
       <c r="E142" t="n">
         <v>0.54</v>
       </c>
       <c r="F142" t="n">
-        <v>0.9818181818181818</v>
+        <v>0.574468085106383</v>
       </c>
       <c r="G142" t="n">
         <v>1.044487427466151</v>
@@ -7307,16 +7307,16 @@
         <v>0.02300000000000002</v>
       </c>
       <c r="J142" t="n">
-        <v>3.300000000000002</v>
+        <v>1.0575</v>
       </c>
       <c r="K142" t="n">
-        <v>0.09465020576131696</v>
+        <v>0.7098765432098765</v>
       </c>
       <c r="L142" t="n">
         <v>0.568421052631579</v>
       </c>
       <c r="M142" t="n">
-        <v>0.6969696969696971</v>
+        <v>0.05437352245862886</v>
       </c>
       <c r="N142" t="n">
         <v>0.7781431334622824</v>
@@ -7325,25 +7325,25 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
           <t>frozenset({'Pemrograman CMS'})</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
-        </is>
-      </c>
       <c r="C143" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D143" t="n">
         <v>0.9399999999999999</v>
-      </c>
-      <c r="D143" t="n">
-        <v>0.55</v>
       </c>
       <c r="E143" t="n">
         <v>0.54</v>
       </c>
       <c r="F143" t="n">
-        <v>0.574468085106383</v>
+        <v>0.9818181818181818</v>
       </c>
       <c r="G143" t="n">
         <v>1.044487427466151</v>
@@ -7355,16 +7355,16 @@
         <v>0.02300000000000002</v>
       </c>
       <c r="J143" t="n">
-        <v>1.0575</v>
+        <v>3.300000000000002</v>
       </c>
       <c r="K143" t="n">
-        <v>0.7098765432098765</v>
+        <v>0.09465020576131696</v>
       </c>
       <c r="L143" t="n">
         <v>0.568421052631579</v>
       </c>
       <c r="M143" t="n">
-        <v>0.05437352245862886</v>
+        <v>0.6969696969696971</v>
       </c>
       <c r="N143" t="n">
         <v>0.7781431334622824</v>
@@ -7373,25 +7373,25 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
+          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
           <t>frozenset({'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>frozenset({'Data mining'})</t>
-        </is>
-      </c>
       <c r="C144" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D144" t="n">
         <v>0.6</v>
       </c>
-      <c r="D144" t="n">
-        <v>0.64</v>
-      </c>
       <c r="E144" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="F144" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.625</v>
       </c>
       <c r="G144" t="n">
         <v>1.041666666666667</v>
@@ -7400,22 +7400,22 @@
         <v>1</v>
       </c>
       <c r="I144" t="n">
-        <v>0.01600000000000001</v>
+        <v>0.006000000000000005</v>
       </c>
       <c r="J144" t="n">
-        <v>1.08</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="K144" t="n">
-        <v>0.1000000000000001</v>
+        <v>0.05263157894736847</v>
       </c>
       <c r="L144" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="M144" t="n">
-        <v>0.07407407407407425</v>
+        <v>0.06250000000000006</v>
       </c>
       <c r="N144" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="145">
@@ -7469,7 +7469,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -7517,25 +7517,25 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Data mining'})</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>0.24</v>
+        <v>0.6</v>
       </c>
       <c r="D147" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="E147" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="F147" t="n">
-        <v>0.625</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="G147" t="n">
         <v>1.041666666666667</v>
@@ -7544,28 +7544,28 @@
         <v>1</v>
       </c>
       <c r="I147" t="n">
-        <v>0.006000000000000005</v>
+        <v>0.01600000000000001</v>
       </c>
       <c r="J147" t="n">
-        <v>1.066666666666667</v>
+        <v>1.08</v>
       </c>
       <c r="K147" t="n">
-        <v>0.05263157894736847</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="L147" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="M147" t="n">
-        <v>0.06250000000000006</v>
+        <v>0.07407407407407425</v>
       </c>
       <c r="N147" t="n">
-        <v>0.4375</v>
+        <v>0.6458333333333334</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7613,7 +7613,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7622,13 +7622,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="D149" t="n">
         <v>0.64</v>
       </c>
       <c r="E149" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="F149" t="n">
         <v>0.6666666666666666</v>
@@ -7640,28 +7640,28 @@
         <v>1</v>
       </c>
       <c r="I149" t="n">
-        <v>0.009599999999999997</v>
+        <v>0.008799999999999975</v>
       </c>
       <c r="J149" t="n">
         <v>1.08</v>
       </c>
       <c r="K149" t="n">
-        <v>0.06249999999999999</v>
+        <v>0.05970149253731327</v>
       </c>
       <c r="L149" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.2933333333333333</v>
       </c>
       <c r="M149" t="n">
         <v>0.07407407407407393</v>
       </c>
       <c r="N149" t="n">
-        <v>0.5208333333333333</v>
+        <v>0.5052083333333333</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="D150" t="n">
         <v>0.64</v>
       </c>
       <c r="E150" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="F150" t="n">
         <v>0.6666666666666666</v>
@@ -7688,33 +7688,33 @@
         <v>1</v>
       </c>
       <c r="I150" t="n">
-        <v>0.008799999999999975</v>
+        <v>0.009599999999999997</v>
       </c>
       <c r="J150" t="n">
         <v>1.08</v>
       </c>
       <c r="K150" t="n">
-        <v>0.05970149253731327</v>
+        <v>0.06249999999999999</v>
       </c>
       <c r="L150" t="n">
-        <v>0.2933333333333333</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="M150" t="n">
         <v>0.07407407407407393</v>
       </c>
       <c r="N150" t="n">
-        <v>0.5052083333333333</v>
+        <v>0.5208333333333333</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -7805,7 +7805,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -8045,25 +8045,25 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
           <t>frozenset({'Data mining'})</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
-        </is>
-      </c>
       <c r="C158" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D158" t="n">
         <v>0.64</v>
-      </c>
-      <c r="D158" t="n">
-        <v>0.82</v>
       </c>
       <c r="E158" t="n">
         <v>0.54</v>
       </c>
       <c r="F158" t="n">
-        <v>0.84375</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="G158" t="n">
         <v>1.028963414634146</v>
@@ -8075,16 +8075,16 @@
         <v>0.0152000000000001</v>
       </c>
       <c r="J158" t="n">
-        <v>1.152</v>
+        <v>1.054285714285714</v>
       </c>
       <c r="K158" t="n">
-        <v>0.07818930041152315</v>
+        <v>0.1563786008230462</v>
       </c>
       <c r="L158" t="n">
         <v>0.5869565217391305</v>
       </c>
       <c r="M158" t="n">
-        <v>0.1319444444444447</v>
+        <v>0.0514905149051491</v>
       </c>
       <c r="N158" t="n">
         <v>0.7511432926829269</v>
@@ -8093,25 +8093,25 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Data mining'})</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C159" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D159" t="n">
         <v>0.82</v>
-      </c>
-      <c r="D159" t="n">
-        <v>0.64</v>
       </c>
       <c r="E159" t="n">
         <v>0.54</v>
       </c>
       <c r="F159" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.84375</v>
       </c>
       <c r="G159" t="n">
         <v>1.028963414634146</v>
@@ -8123,16 +8123,16 @@
         <v>0.0152000000000001</v>
       </c>
       <c r="J159" t="n">
-        <v>1.054285714285714</v>
+        <v>1.152</v>
       </c>
       <c r="K159" t="n">
-        <v>0.1563786008230462</v>
+        <v>0.07818930041152315</v>
       </c>
       <c r="L159" t="n">
         <v>0.5869565217391305</v>
       </c>
       <c r="M159" t="n">
-        <v>0.0514905149051491</v>
+        <v>0.1319444444444447</v>
       </c>
       <c r="N159" t="n">
         <v>0.7511432926829269</v>
@@ -8141,7 +8141,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -8237,7 +8237,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -8285,7 +8285,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -8333,7 +8333,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -8429,25 +8429,25 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
+          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
           <t>frozenset({'Game Edukasi'})</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
-        </is>
-      </c>
       <c r="C166" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D166" t="n">
         <v>0.62</v>
-      </c>
-      <c r="D166" t="n">
-        <v>0.63</v>
       </c>
       <c r="E166" t="n">
         <v>0.4</v>
       </c>
       <c r="F166" t="n">
-        <v>0.6451612903225807</v>
+        <v>0.634920634920635</v>
       </c>
       <c r="G166" t="n">
         <v>1.024065540194573</v>
@@ -8459,16 +8459,16 @@
         <v>0.009400000000000019</v>
       </c>
       <c r="J166" t="n">
-        <v>1.042727272727273</v>
+        <v>1.040869565217392</v>
       </c>
       <c r="K166" t="n">
-        <v>0.06184210526315801</v>
+        <v>0.06351351351351364</v>
       </c>
       <c r="L166" t="n">
         <v>0.4705882352941177</v>
       </c>
       <c r="M166" t="n">
-        <v>0.04097646033129928</v>
+        <v>0.03926482873851316</v>
       </c>
       <c r="N166" t="n">
         <v>0.6400409626216079</v>
@@ -8477,25 +8477,25 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
+          <t>frozenset({'Game Edukasi'})</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
           <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>frozenset({'Game Edukasi'})</t>
-        </is>
-      </c>
       <c r="C167" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D167" t="n">
         <v>0.63</v>
-      </c>
-      <c r="D167" t="n">
-        <v>0.62</v>
       </c>
       <c r="E167" t="n">
         <v>0.4</v>
       </c>
       <c r="F167" t="n">
-        <v>0.634920634920635</v>
+        <v>0.6451612903225807</v>
       </c>
       <c r="G167" t="n">
         <v>1.024065540194573</v>
@@ -8507,16 +8507,16 @@
         <v>0.009400000000000019</v>
       </c>
       <c r="J167" t="n">
-        <v>1.040869565217392</v>
+        <v>1.042727272727273</v>
       </c>
       <c r="K167" t="n">
-        <v>0.06351351351351364</v>
+        <v>0.06184210526315801</v>
       </c>
       <c r="L167" t="n">
         <v>0.4705882352941177</v>
       </c>
       <c r="M167" t="n">
-        <v>0.03926482873851316</v>
+        <v>0.04097646033129928</v>
       </c>
       <c r="N167" t="n">
         <v>0.6400409626216079</v>
@@ -8525,7 +8525,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -8573,7 +8573,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -8669,12 +8669,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -8717,12 +8717,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -8813,7 +8813,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -9149,7 +9149,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -9245,25 +9245,25 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Data mining'})</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>0.16</v>
+        <v>0.51</v>
       </c>
       <c r="D183" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="E183" t="n">
-        <v>0.11</v>
+        <v>0.33</v>
       </c>
       <c r="F183" t="n">
-        <v>0.6875</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="G183" t="n">
         <v>1.011029411764706</v>
@@ -9272,22 +9272,22 @@
         <v>1</v>
       </c>
       <c r="I183" t="n">
-        <v>0.001199999999999993</v>
+        <v>0.003599999999999992</v>
       </c>
       <c r="J183" t="n">
-        <v>1.024</v>
+        <v>1.02</v>
       </c>
       <c r="K183" t="n">
-        <v>0.01298701298701291</v>
+        <v>0.02226345083487936</v>
       </c>
       <c r="L183" t="n">
-        <v>0.1506849315068493</v>
+        <v>0.402439024390244</v>
       </c>
       <c r="M183" t="n">
-        <v>0.02343749999999985</v>
+        <v>0.01960784313725496</v>
       </c>
       <c r="N183" t="n">
-        <v>0.4246323529411765</v>
+        <v>0.5813419117647058</v>
       </c>
     </row>
     <row r="184">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -9341,25 +9341,25 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Desain Grafis', 'Data mining'})</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining'})</t>
+          <t>frozenset({'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>0.51</v>
+        <v>0.16</v>
       </c>
       <c r="D185" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="E185" t="n">
-        <v>0.33</v>
+        <v>0.11</v>
       </c>
       <c r="F185" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.6875</v>
       </c>
       <c r="G185" t="n">
         <v>1.011029411764706</v>
@@ -9368,28 +9368,28 @@
         <v>1</v>
       </c>
       <c r="I185" t="n">
-        <v>0.003599999999999992</v>
+        <v>0.001199999999999993</v>
       </c>
       <c r="J185" t="n">
-        <v>1.02</v>
+        <v>1.024</v>
       </c>
       <c r="K185" t="n">
-        <v>0.02226345083487936</v>
+        <v>0.01298701298701291</v>
       </c>
       <c r="L185" t="n">
-        <v>0.402439024390244</v>
+        <v>0.1506849315068493</v>
       </c>
       <c r="M185" t="n">
-        <v>0.01960784313725496</v>
+        <v>0.02343749999999985</v>
       </c>
       <c r="N185" t="n">
-        <v>0.5813419117647058</v>
+        <v>0.4246323529411765</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining'})</t>
+          <t>frozenset({'Desain Grafis', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -9437,7 +9437,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -9533,7 +9533,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -9581,7 +9581,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -9590,13 +9590,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>0.64</v>
+        <v>0.24</v>
       </c>
       <c r="D190" t="n">
         <v>0.62</v>
       </c>
       <c r="E190" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="F190" t="n">
         <v>0.625</v>
@@ -9608,28 +9608,28 @@
         <v>1</v>
       </c>
       <c r="I190" t="n">
-        <v>0.003200000000000036</v>
+        <v>0.001200000000000007</v>
       </c>
       <c r="J190" t="n">
         <v>1.013333333333333</v>
       </c>
       <c r="K190" t="n">
-        <v>0.02222222222222248</v>
+        <v>0.01052631578947374</v>
       </c>
       <c r="L190" t="n">
-        <v>0.4651162790697675</v>
+        <v>0.2112676056338028</v>
       </c>
       <c r="M190" t="n">
         <v>0.01315789473684212</v>
       </c>
       <c r="N190" t="n">
-        <v>0.6350806451612904</v>
+        <v>0.4334677419354839</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining'})</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -9638,13 +9638,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>0.24</v>
+        <v>0.64</v>
       </c>
       <c r="D191" t="n">
         <v>0.62</v>
       </c>
       <c r="E191" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="F191" t="n">
         <v>0.625</v>
@@ -9656,28 +9656,28 @@
         <v>1</v>
       </c>
       <c r="I191" t="n">
-        <v>0.001200000000000007</v>
+        <v>0.003200000000000036</v>
       </c>
       <c r="J191" t="n">
         <v>1.013333333333333</v>
       </c>
       <c r="K191" t="n">
-        <v>0.01052631578947374</v>
+        <v>0.02222222222222248</v>
       </c>
       <c r="L191" t="n">
-        <v>0.2112676056338028</v>
+        <v>0.4651162790697675</v>
       </c>
       <c r="M191" t="n">
         <v>0.01315789473684212</v>
       </c>
       <c r="N191" t="n">
-        <v>0.4334677419354839</v>
+        <v>0.6350806451612904</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>frozenset({'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Desain Grafis', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -9686,13 +9686,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
       <c r="D192" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E192" t="n">
-        <v>0.36</v>
+        <v>0.18</v>
       </c>
       <c r="F192" t="n">
         <v>0.9473684210526315</v>
@@ -9704,28 +9704,28 @@
         <v>1</v>
       </c>
       <c r="I192" t="n">
-        <v>0.002800000000000025</v>
+        <v>0.001400000000000012</v>
       </c>
       <c r="J192" t="n">
         <v>1.14</v>
       </c>
       <c r="K192" t="n">
-        <v>0.01254480286738362</v>
+        <v>0.009602194787380057</v>
       </c>
       <c r="L192" t="n">
-        <v>0.3750000000000001</v>
+        <v>0.1894736842105263</v>
       </c>
       <c r="M192" t="n">
         <v>0.1228070175438595</v>
       </c>
       <c r="N192" t="n">
-        <v>0.6651735722284434</v>
+        <v>0.5694288913773796</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -9734,13 +9734,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
       <c r="D193" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E193" t="n">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="F193" t="n">
         <v>0.9473684210526315</v>
@@ -9752,22 +9752,22 @@
         <v>1</v>
       </c>
       <c r="I193" t="n">
-        <v>0.001400000000000012</v>
+        <v>0.002800000000000025</v>
       </c>
       <c r="J193" t="n">
         <v>1.14</v>
       </c>
       <c r="K193" t="n">
-        <v>0.009602194787380057</v>
+        <v>0.01254480286738362</v>
       </c>
       <c r="L193" t="n">
-        <v>0.1894736842105263</v>
+        <v>0.3750000000000001</v>
       </c>
       <c r="M193" t="n">
         <v>0.1228070175438595</v>
       </c>
       <c r="N193" t="n">
-        <v>0.5694288913773796</v>
+        <v>0.6651735722284434</v>
       </c>
     </row>
     <row r="194">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -9821,7 +9821,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -9917,7 +9917,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -10013,7 +10013,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -10061,7 +10061,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -10109,25 +10109,25 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C201" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D201" t="n">
         <v>0.82</v>
-      </c>
-      <c r="D201" t="n">
-        <v>0.62</v>
       </c>
       <c r="E201" t="n">
         <v>0.51</v>
       </c>
       <c r="F201" t="n">
-        <v>0.6219512195121951</v>
+        <v>0.8225806451612904</v>
       </c>
       <c r="G201" t="n">
         <v>1.003147128245476</v>
@@ -10139,16 +10139,16 @@
         <v>0.001600000000000046</v>
       </c>
       <c r="J201" t="n">
-        <v>1.005161290322581</v>
+        <v>1.014545454545455</v>
       </c>
       <c r="K201" t="n">
-        <v>0.01742919389978263</v>
+        <v>0.008255933952528617</v>
       </c>
       <c r="L201" t="n">
         <v>0.5483870967741936</v>
       </c>
       <c r="M201" t="n">
-        <v>0.005134788189987168</v>
+        <v>0.01433691756272454</v>
       </c>
       <c r="N201" t="n">
         <v>0.7222659323367427</v>
@@ -10157,25 +10157,25 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
           <t>frozenset({'Game Edukasi'})</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
-        </is>
-      </c>
       <c r="C202" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D202" t="n">
         <v>0.62</v>
-      </c>
-      <c r="D202" t="n">
-        <v>0.82</v>
       </c>
       <c r="E202" t="n">
         <v>0.51</v>
       </c>
       <c r="F202" t="n">
-        <v>0.8225806451612904</v>
+        <v>0.6219512195121951</v>
       </c>
       <c r="G202" t="n">
         <v>1.003147128245476</v>
@@ -10187,16 +10187,16 @@
         <v>0.001600000000000046</v>
       </c>
       <c r="J202" t="n">
-        <v>1.014545454545455</v>
+        <v>1.005161290322581</v>
       </c>
       <c r="K202" t="n">
-        <v>0.008255933952528617</v>
+        <v>0.01742919389978263</v>
       </c>
       <c r="L202" t="n">
         <v>0.5483870967741936</v>
       </c>
       <c r="M202" t="n">
-        <v>0.01433691756272454</v>
+        <v>0.005134788189987168</v>
       </c>
       <c r="N202" t="n">
         <v>0.7222659323367427</v>
@@ -10301,7 +10301,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -10349,25 +10349,25 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
+          <t>frozenset({'Teknologi IoT'})</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
           <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
-        </is>
-      </c>
       <c r="C206" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D206" t="n">
         <v>0.63</v>
       </c>
-      <c r="D206" t="n">
-        <v>0.57</v>
-      </c>
       <c r="E206" t="n">
-        <v>0.36</v>
+        <v>0.24</v>
       </c>
       <c r="F206" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="G206" t="n">
         <v>1.00250626566416</v>
@@ -10376,43 +10376,43 @@
         <v>1</v>
       </c>
       <c r="I206" t="n">
-        <v>0.0009000000000000119</v>
+        <v>0.0005999999999999894</v>
       </c>
       <c r="J206" t="n">
-        <v>1.003333333333333</v>
+        <v>1.004285714285714</v>
       </c>
       <c r="K206" t="n">
-        <v>0.006756756756756846</v>
+        <v>0.004032258064516059</v>
       </c>
       <c r="L206" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.3116883116883117</v>
       </c>
       <c r="M206" t="n">
-        <v>0.003322259136212664</v>
+        <v>0.004267425320056792</v>
       </c>
       <c r="N206" t="n">
-        <v>0.6015037593984962</v>
+        <v>0.506265664160401</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>0.21</v>
+        <v>0.63</v>
       </c>
       <c r="D207" t="n">
         <v>0.57</v>
       </c>
       <c r="E207" t="n">
-        <v>0.12</v>
+        <v>0.36</v>
       </c>
       <c r="F207" t="n">
         <v>0.5714285714285714</v>
@@ -10424,46 +10424,46 @@
         <v>1</v>
       </c>
       <c r="I207" t="n">
-        <v>0.0003000000000000086</v>
+        <v>0.0009000000000000119</v>
       </c>
       <c r="J207" t="n">
         <v>1.003333333333333</v>
       </c>
       <c r="K207" t="n">
-        <v>0.003164556962025407</v>
+        <v>0.006756756756756846</v>
       </c>
       <c r="L207" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="M207" t="n">
         <v>0.003322259136212664</v>
       </c>
       <c r="N207" t="n">
-        <v>0.3909774436090225</v>
+        <v>0.6015037593984962</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>frozenset({'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>0.38</v>
+        <v>0.21</v>
       </c>
       <c r="D208" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="E208" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="F208" t="n">
-        <v>0.631578947368421</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="G208" t="n">
         <v>1.00250626566416</v>
@@ -10472,22 +10472,22 @@
         <v>1</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0005999999999999894</v>
+        <v>0.0003000000000000086</v>
       </c>
       <c r="J208" t="n">
-        <v>1.004285714285714</v>
+        <v>1.003333333333333</v>
       </c>
       <c r="K208" t="n">
-        <v>0.004032258064516059</v>
+        <v>0.003164556962025407</v>
       </c>
       <c r="L208" t="n">
-        <v>0.3116883116883117</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="M208" t="n">
-        <v>0.004267425320056792</v>
+        <v>0.003322259136212664</v>
       </c>
       <c r="N208" t="n">
-        <v>0.506265664160401</v>
+        <v>0.3909774436090225</v>
       </c>
     </row>
     <row r="209">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -10541,25 +10541,25 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="D210" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="E210" t="n">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="F210" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="G210" t="n">
         <v>1</v>
@@ -10577,37 +10577,37 @@
         <v>0</v>
       </c>
       <c r="L210" t="n">
-        <v>0.3291139240506329</v>
+        <v>0.402439024390244</v>
       </c>
       <c r="M210" t="n">
         <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>0.525</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D211" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="E211" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="F211" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="G211" t="n">
         <v>1</v>
@@ -10625,37 +10625,37 @@
         <v>0</v>
       </c>
       <c r="L211" t="n">
-        <v>0.2191780821917808</v>
+        <v>0.3291139240506329</v>
       </c>
       <c r="M211" t="n">
         <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>0.445</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Data mining'})</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>0.55</v>
+        <v>0.25</v>
       </c>
       <c r="D212" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="E212" t="n">
-        <v>0.33</v>
+        <v>0.16</v>
       </c>
       <c r="F212" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="G212" t="n">
         <v>1</v>
@@ -10673,19 +10673,19 @@
         <v>0</v>
       </c>
       <c r="L212" t="n">
-        <v>0.402439024390244</v>
+        <v>0.2191780821917808</v>
       </c>
       <c r="M212" t="n">
         <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>0.575</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -10829,7 +10829,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -10877,7 +10877,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -10925,7 +10925,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -10973,7 +10973,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -11069,7 +11069,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -11117,7 +11117,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -11165,7 +11165,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -11261,7 +11261,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -11309,7 +11309,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -11453,12 +11453,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -11501,25 +11501,25 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
           <t>frozenset({'Data mining'})</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
-        </is>
-      </c>
       <c r="C230" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="D230" t="n">
         <v>0.64</v>
-      </c>
-      <c r="D230" t="n">
-        <v>0.57</v>
       </c>
       <c r="E230" t="n">
         <v>0.36</v>
       </c>
       <c r="F230" t="n">
-        <v>0.5625</v>
+        <v>0.6315789473684211</v>
       </c>
       <c r="G230" t="n">
         <v>0.986842105263158</v>
@@ -11531,16 +11531,16 @@
         <v>-0.004799999999999971</v>
       </c>
       <c r="J230" t="n">
-        <v>0.982857142857143</v>
+        <v>0.9771428571428573</v>
       </c>
       <c r="K230" t="n">
-        <v>-0.0357142857142855</v>
+        <v>-0.03007518796992463</v>
       </c>
       <c r="L230" t="n">
         <v>0.4235294117647059</v>
       </c>
       <c r="M230" t="n">
-        <v>-0.01744186046511616</v>
+        <v>-0.0233918128654969</v>
       </c>
       <c r="N230" t="n">
         <v>0.5970394736842106</v>
@@ -11549,25 +11549,25 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Data mining'})</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="C231" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D231" t="n">
         <v>0.57</v>
-      </c>
-      <c r="D231" t="n">
-        <v>0.64</v>
       </c>
       <c r="E231" t="n">
         <v>0.36</v>
       </c>
       <c r="F231" t="n">
-        <v>0.6315789473684211</v>
+        <v>0.5625</v>
       </c>
       <c r="G231" t="n">
         <v>0.986842105263158</v>
@@ -11579,16 +11579,16 @@
         <v>-0.004799999999999971</v>
       </c>
       <c r="J231" t="n">
-        <v>0.9771428571428573</v>
+        <v>0.982857142857143</v>
       </c>
       <c r="K231" t="n">
-        <v>-0.03007518796992463</v>
+        <v>-0.0357142857142855</v>
       </c>
       <c r="L231" t="n">
         <v>0.4235294117647059</v>
       </c>
       <c r="M231" t="n">
-        <v>-0.0233918128654969</v>
+        <v>-0.01744186046511616</v>
       </c>
       <c r="N231" t="n">
         <v>0.5970394736842106</v>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -11693,7 +11693,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -11789,7 +11789,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -11933,7 +11933,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -11981,7 +11981,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -12077,25 +12077,25 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
+          <t>frozenset({'Game Edukasi'})</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
           <t>frozenset({'Realitas Virtual'})</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>frozenset({'Game Edukasi'})</t>
-        </is>
-      </c>
       <c r="C242" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D242" t="n">
         <v>0.87</v>
-      </c>
-      <c r="D242" t="n">
-        <v>0.62</v>
       </c>
       <c r="E242" t="n">
         <v>0.53</v>
       </c>
       <c r="F242" t="n">
-        <v>0.6091954022988506</v>
+        <v>0.8548387096774194</v>
       </c>
       <c r="G242" t="n">
         <v>0.9825732295142752</v>
@@ -12107,16 +12107,16 @@
         <v>-0.009399999999999964</v>
       </c>
       <c r="J242" t="n">
-        <v>0.9723529411764706</v>
+        <v>0.8955555555555557</v>
       </c>
       <c r="K242" t="n">
-        <v>-0.1200510855683265</v>
+        <v>-0.04459203036053114</v>
       </c>
       <c r="L242" t="n">
         <v>0.5520833333333334</v>
       </c>
       <c r="M242" t="n">
-        <v>-0.02843315184512997</v>
+        <v>-0.1166253101736971</v>
       </c>
       <c r="N242" t="n">
         <v>0.7320170559881349</v>
@@ -12125,25 +12125,25 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
+          <t>frozenset({'Realitas Virtual'})</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
           <t>frozenset({'Game Edukasi'})</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>frozenset({'Realitas Virtual'})</t>
-        </is>
-      </c>
       <c r="C243" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="D243" t="n">
         <v>0.62</v>
-      </c>
-      <c r="D243" t="n">
-        <v>0.87</v>
       </c>
       <c r="E243" t="n">
         <v>0.53</v>
       </c>
       <c r="F243" t="n">
-        <v>0.8548387096774194</v>
+        <v>0.6091954022988506</v>
       </c>
       <c r="G243" t="n">
         <v>0.9825732295142752</v>
@@ -12155,16 +12155,16 @@
         <v>-0.009399999999999964</v>
       </c>
       <c r="J243" t="n">
-        <v>0.8955555555555557</v>
+        <v>0.9723529411764706</v>
       </c>
       <c r="K243" t="n">
-        <v>-0.04459203036053114</v>
+        <v>-0.1200510855683265</v>
       </c>
       <c r="L243" t="n">
         <v>0.5520833333333334</v>
       </c>
       <c r="M243" t="n">
-        <v>-0.1166253101736971</v>
+        <v>-0.02843315184512997</v>
       </c>
       <c r="N243" t="n">
         <v>0.7320170559881349</v>
@@ -12173,7 +12173,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Desain Grafis', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12221,7 +12221,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan', 'Data mining'})</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12269,7 +12269,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Game Edukasi', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Data mining'})</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12317,7 +12317,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12326,13 +12326,13 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="D247" t="n">
         <v>0.68</v>
       </c>
       <c r="E247" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="F247" t="n">
         <v>0.6666666666666667</v>
@@ -12344,22 +12344,22 @@
         <v>1</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.003200000000000008</v>
+        <v>-0.002799999999999997</v>
       </c>
       <c r="J247" t="n">
         <v>0.9600000000000001</v>
       </c>
       <c r="K247" t="n">
-        <v>-0.02564102564102571</v>
+        <v>-0.02469135802469133</v>
       </c>
       <c r="L247" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1866666666666667</v>
       </c>
       <c r="M247" t="n">
         <v>-0.04166666666666659</v>
       </c>
       <c r="N247" t="n">
-        <v>0.4509803921568628</v>
+        <v>0.4362745098039216</v>
       </c>
     </row>
     <row r="248">
@@ -12413,7 +12413,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -12461,7 +12461,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -12509,7 +12509,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -12518,13 +12518,13 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="D251" t="n">
         <v>0.68</v>
       </c>
       <c r="E251" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="F251" t="n">
         <v>0.6666666666666667</v>
@@ -12536,28 +12536,28 @@
         <v>1</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.002799999999999997</v>
+        <v>-0.003200000000000008</v>
       </c>
       <c r="J251" t="n">
         <v>0.9600000000000001</v>
       </c>
       <c r="K251" t="n">
-        <v>-0.02469135802469133</v>
+        <v>-0.02564102564102571</v>
       </c>
       <c r="L251" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="M251" t="n">
         <v>-0.04166666666666659</v>
       </c>
       <c r="N251" t="n">
-        <v>0.4362745098039216</v>
+        <v>0.4509803921568628</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -12566,13 +12566,13 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>0.33</v>
+        <v>0.18</v>
       </c>
       <c r="D252" t="n">
         <v>0.68</v>
       </c>
       <c r="E252" t="n">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="F252" t="n">
         <v>0.6666666666666666</v>
@@ -12584,28 +12584,28 @@
         <v>1</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.004400000000000015</v>
+        <v>-0.002400000000000013</v>
       </c>
       <c r="J252" t="n">
         <v>0.9599999999999997</v>
       </c>
       <c r="K252" t="n">
-        <v>-0.02898550724637691</v>
+        <v>-0.02380952380952394</v>
       </c>
       <c r="L252" t="n">
-        <v>0.2784810126582278</v>
+        <v>0.1621621621621621</v>
       </c>
       <c r="M252" t="n">
         <v>-0.04166666666666694</v>
       </c>
       <c r="N252" t="n">
-        <v>0.4950980392156862</v>
+        <v>0.4215686274509803</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -12653,7 +12653,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -12662,13 +12662,13 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="D254" t="n">
         <v>0.68</v>
       </c>
       <c r="E254" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="F254" t="n">
         <v>0.6666666666666666</v>
@@ -12680,22 +12680,22 @@
         <v>1</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.002400000000000013</v>
+        <v>-0.004400000000000015</v>
       </c>
       <c r="J254" t="n">
         <v>0.9599999999999997</v>
       </c>
       <c r="K254" t="n">
-        <v>-0.02380952380952394</v>
+        <v>-0.02898550724637691</v>
       </c>
       <c r="L254" t="n">
-        <v>0.1621621621621621</v>
+        <v>0.2784810126582278</v>
       </c>
       <c r="M254" t="n">
         <v>-0.04166666666666694</v>
       </c>
       <c r="N254" t="n">
-        <v>0.4215686274509803</v>
+        <v>0.4950980392156862</v>
       </c>
     </row>
     <row r="255">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -12749,7 +12749,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -12941,7 +12941,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Game Edukasi', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -13085,7 +13085,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13133,12 +13133,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -13229,7 +13229,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13325,7 +13325,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -13565,7 +13565,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13661,7 +13661,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13709,12 +13709,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Game Edukasi', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -13949,7 +13949,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -14002,7 +14002,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -14141,12 +14141,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -14194,7 +14194,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -14237,7 +14237,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -14285,7 +14285,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi'})</t>
+          <t>frozenset({'Game Edukasi', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -14333,7 +14333,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Game Edukasi', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -14429,7 +14429,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -14477,12 +14477,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -14525,7 +14525,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -14621,7 +14621,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -14669,7 +14669,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -14717,7 +14717,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi'})</t>
+          <t>frozenset({'Game Edukasi', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -14813,7 +14813,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -14861,7 +14861,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -14909,7 +14909,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -14957,7 +14957,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -15005,7 +15005,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -15149,7 +15149,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -15197,7 +15197,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -15293,7 +15293,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -15341,7 +15341,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -15389,12 +15389,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -15437,12 +15437,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -15490,7 +15490,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -15533,7 +15533,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -15581,7 +15581,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -15725,22 +15725,22 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Game Edukasi'})</t>
+          <t>frozenset({'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="D318" t="n">
         <v>0.82</v>
       </c>
       <c r="E318" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="F318" t="n">
         <v>0.75</v>
@@ -15752,43 +15752,43 @@
         <v>1</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.01679999999999998</v>
+        <v>-0.02239999999999998</v>
       </c>
       <c r="J318" t="n">
         <v>0.7200000000000002</v>
       </c>
       <c r="K318" t="n">
-        <v>-0.1093749999999999</v>
+        <v>-0.1206896551724137</v>
       </c>
       <c r="L318" t="n">
-        <v>0.2045454545454545</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="M318" t="n">
         <v>-0.3888888888888885</v>
       </c>
       <c r="N318" t="n">
-        <v>0.4847560975609756</v>
+        <v>0.5213414634146342</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis'})</t>
+          <t>frozenset({'Desain Grafis', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="D319" t="n">
         <v>0.82</v>
       </c>
       <c r="E319" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="F319" t="n">
         <v>0.75</v>
@@ -15800,22 +15800,22 @@
         <v>1</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.02239999999999998</v>
+        <v>-0.01679999999999998</v>
       </c>
       <c r="J319" t="n">
         <v>0.7200000000000002</v>
       </c>
       <c r="K319" t="n">
-        <v>-0.1206896551724137</v>
+        <v>-0.1093749999999999</v>
       </c>
       <c r="L319" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2045454545454545</v>
       </c>
       <c r="M319" t="n">
         <v>-0.3888888888888885</v>
       </c>
       <c r="N319" t="n">
-        <v>0.5213414634146342</v>
+        <v>0.4847560975609756</v>
       </c>
     </row>
     <row r="320">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -15869,7 +15869,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -15965,12 +15965,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -16013,7 +16013,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -16061,25 +16061,25 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
+          <t>frozenset({'Pengolahan Citra Digital'})</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
           <t>frozenset({'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>frozenset({'Pengolahan Citra Digital'})</t>
-        </is>
-      </c>
       <c r="C325" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D325" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D325" t="n">
-        <v>0.68</v>
       </c>
       <c r="E325" t="n">
         <v>0.37</v>
       </c>
       <c r="F325" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.5441176470588235</v>
       </c>
       <c r="G325" t="n">
         <v>0.9068627450980392</v>
@@ -16091,16 +16091,16 @@
         <v>-0.03800000000000003</v>
       </c>
       <c r="J325" t="n">
-        <v>0.8347826086956521</v>
+        <v>0.8774193548387096</v>
       </c>
       <c r="K325" t="n">
-        <v>-0.2043010752688174</v>
+        <v>-0.2429667519181588</v>
       </c>
       <c r="L325" t="n">
         <v>0.4065934065934066</v>
       </c>
       <c r="M325" t="n">
-        <v>-0.1979166666666668</v>
+        <v>-0.1397058823529412</v>
       </c>
       <c r="N325" t="n">
         <v>0.580392156862745</v>
@@ -16109,25 +16109,25 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
+          <t>frozenset({'Game Edukasi', 'Pemrograman CMS'})</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
           <t>frozenset({'Pengolahan Citra Digital'})</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS'})</t>
-        </is>
-      </c>
       <c r="C326" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D326" t="n">
         <v>0.68</v>
-      </c>
-      <c r="D326" t="n">
-        <v>0.6</v>
       </c>
       <c r="E326" t="n">
         <v>0.37</v>
       </c>
       <c r="F326" t="n">
-        <v>0.5441176470588235</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="G326" t="n">
         <v>0.9068627450980392</v>
@@ -16139,16 +16139,16 @@
         <v>-0.03800000000000003</v>
       </c>
       <c r="J326" t="n">
-        <v>0.8774193548387096</v>
+        <v>0.8347826086956521</v>
       </c>
       <c r="K326" t="n">
-        <v>-0.2429667519181588</v>
+        <v>-0.2043010752688174</v>
       </c>
       <c r="L326" t="n">
         <v>0.4065934065934066</v>
       </c>
       <c r="M326" t="n">
-        <v>-0.1397058823529412</v>
+        <v>-0.1979166666666668</v>
       </c>
       <c r="N326" t="n">
         <v>0.580392156862745</v>
@@ -16349,7 +16349,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Desain Grafis', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -16397,7 +16397,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Game Edukasi', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Game Edukasi', 'Desain Grafis', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -16445,7 +16445,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -16493,7 +16493,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -16541,7 +16541,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -16637,12 +16637,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -16685,7 +16685,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -16733,7 +16733,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -16781,7 +16781,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -16829,7 +16829,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Game Edukasi', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Game Edukasi', 'Desain Grafis', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -16925,7 +16925,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -16973,7 +16973,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -17165,7 +17165,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining'})</t>
+          <t>frozenset({'Desain Grafis', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -17213,7 +17213,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Desain Grafis', 'Data mining'})</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -17357,7 +17357,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -17405,7 +17405,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -17453,7 +17453,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -17501,7 +17501,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -17549,7 +17549,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -17597,7 +17597,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -17645,7 +17645,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -17693,7 +17693,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -17741,7 +17741,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -17837,7 +17837,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -17885,7 +17885,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -17933,7 +17933,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Game Edukasi', 'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -17981,7 +17981,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -18029,7 +18029,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -18077,7 +18077,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -18317,7 +18317,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -18326,13 +18326,13 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="D372" t="n">
         <v>0.63</v>
       </c>
       <c r="E372" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="F372" t="n">
         <v>0.5</v>
@@ -18344,28 +18344,28 @@
         <v>1</v>
       </c>
       <c r="I372" t="n">
-        <v>-0.03120000000000001</v>
+        <v>-0.0416</v>
       </c>
       <c r="J372" t="n">
         <v>0.74</v>
       </c>
       <c r="K372" t="n">
-        <v>-0.2549019607843138</v>
+        <v>-0.276595744680851</v>
       </c>
       <c r="L372" t="n">
-        <v>0.16</v>
+        <v>0.2025316455696203</v>
       </c>
       <c r="M372" t="n">
         <v>-0.3513513513513514</v>
       </c>
       <c r="N372" t="n">
-        <v>0.3452380952380952</v>
+        <v>0.376984126984127</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -18374,13 +18374,13 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="D373" t="n">
         <v>0.63</v>
       </c>
       <c r="E373" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="F373" t="n">
         <v>0.5</v>
@@ -18392,28 +18392,28 @@
         <v>1</v>
       </c>
       <c r="I373" t="n">
-        <v>-0.0416</v>
+        <v>-0.03120000000000001</v>
       </c>
       <c r="J373" t="n">
         <v>0.74</v>
       </c>
       <c r="K373" t="n">
-        <v>-0.276595744680851</v>
+        <v>-0.2549019607843138</v>
       </c>
       <c r="L373" t="n">
-        <v>0.2025316455696203</v>
+        <v>0.16</v>
       </c>
       <c r="M373" t="n">
         <v>-0.3513513513513514</v>
       </c>
       <c r="N373" t="n">
-        <v>0.376984126984127</v>
+        <v>0.3452380952380952</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -18509,7 +18509,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -18518,13 +18518,13 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="D376" t="n">
         <v>0.64</v>
       </c>
       <c r="E376" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="F376" t="n">
         <v>0.5</v>
@@ -18536,28 +18536,28 @@
         <v>1</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.03359999999999999</v>
+        <v>-0.04480000000000001</v>
       </c>
       <c r="J376" t="n">
         <v>0.72</v>
       </c>
       <c r="K376" t="n">
-        <v>-0.2692307692307692</v>
+        <v>-0.2916666666666667</v>
       </c>
       <c r="L376" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.2</v>
       </c>
       <c r="M376" t="n">
         <v>-0.388888888888889</v>
       </c>
       <c r="N376" t="n">
-        <v>0.34375</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis'})</t>
+          <t>frozenset({'Realitas Virtual', 'Desain Grafis', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -18566,13 +18566,13 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="D377" t="n">
         <v>0.64</v>
       </c>
       <c r="E377" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="F377" t="n">
         <v>0.5</v>
@@ -18584,28 +18584,28 @@
         <v>1</v>
       </c>
       <c r="I377" t="n">
-        <v>-0.04480000000000001</v>
+        <v>-0.03359999999999999</v>
       </c>
       <c r="J377" t="n">
         <v>0.72</v>
       </c>
       <c r="K377" t="n">
-        <v>-0.2916666666666667</v>
+        <v>-0.2692307692307692</v>
       </c>
       <c r="L377" t="n">
-        <v>0.2</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="M377" t="n">
         <v>-0.388888888888889</v>
       </c>
       <c r="N377" t="n">
-        <v>0.375</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Game Edukasi'})</t>
+          <t>frozenset({'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -18614,13 +18614,13 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="D378" t="n">
         <v>0.65</v>
       </c>
       <c r="E378" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="F378" t="n">
         <v>0.5</v>
@@ -18632,28 +18632,28 @@
         <v>1</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.036</v>
+        <v>-0.04800000000000001</v>
       </c>
       <c r="J378" t="n">
         <v>0.7</v>
       </c>
       <c r="K378" t="n">
-        <v>-0.2830188679245283</v>
+        <v>-0.306122448979592</v>
       </c>
       <c r="L378" t="n">
-        <v>0.1558441558441558</v>
+        <v>0.1975308641975309</v>
       </c>
       <c r="M378" t="n">
         <v>-0.4285714285714287</v>
       </c>
       <c r="N378" t="n">
-        <v>0.3423076923076923</v>
+        <v>0.3730769230769231</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis'})</t>
+          <t>frozenset({'Desain Grafis', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -18662,13 +18662,13 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="D379" t="n">
         <v>0.65</v>
       </c>
       <c r="E379" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="F379" t="n">
         <v>0.5</v>
@@ -18680,28 +18680,28 @@
         <v>1</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.04800000000000001</v>
+        <v>-0.036</v>
       </c>
       <c r="J379" t="n">
         <v>0.7</v>
       </c>
       <c r="K379" t="n">
-        <v>-0.306122448979592</v>
+        <v>-0.2830188679245283</v>
       </c>
       <c r="L379" t="n">
-        <v>0.1975308641975309</v>
+        <v>0.1558441558441558</v>
       </c>
       <c r="M379" t="n">
         <v>-0.4285714285714287</v>
       </c>
       <c r="N379" t="n">
-        <v>0.3730769230769231</v>
+        <v>0.3423076923076923</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Game Edukasi', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Game Edukasi', 'Desain Grafis', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>frozenset({'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C381" t="n">

--- a/hasil_aturan_asosiasi.xlsx
+++ b/hasil_aturan_asosiasi.xlsx
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS', 'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Realitas Virtual', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -647,12 +647,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -695,7 +695,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Data mining', 'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Data mining', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -791,7 +791,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining'})</t>
+          <t>frozenset({'Data mining', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -887,25 +887,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="D10" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="E10" t="n">
         <v>0.1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G10" t="n">
         <v>1.322751322751323</v>
@@ -914,46 +914,46 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02439999999999999</v>
+        <v>0.02440000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>1.61</v>
+        <v>2.220000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.283720930232558</v>
+        <v>0.2772727272727273</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1724137931034483</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3788819875776397</v>
+        <v>0.5495495495495496</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4497354497354498</v>
+        <v>0.496031746031746</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="D11" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="E11" t="n">
         <v>0.1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="G11" t="n">
         <v>1.322751322751323</v>
@@ -962,28 +962,28 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02440000000000001</v>
+        <v>0.02439999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>2.220000000000001</v>
+        <v>1.61</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2772727272727273</v>
+        <v>0.283720930232558</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.1724137931034483</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5495495495495496</v>
+        <v>0.3788819875776397</v>
       </c>
       <c r="N11" t="n">
-        <v>0.496031746031746</v>
+        <v>0.4497354497354498</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining'})</t>
+          <t>frozenset({'Data mining', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Data mining', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1127,12 +1127,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Game Edukasi', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining'})</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1175,7 +1175,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1271,7 +1271,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1463,12 +1463,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1511,7 +1511,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1607,25 +1607,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="D25" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="E25" t="n">
         <v>0.14</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7777777777777779</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="G25" t="n">
         <v>1.234567901234568</v>
@@ -1637,43 +1637,43 @@
         <v>0.02660000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>1.665000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2317073170731708</v>
+        <v>0.2405063291139241</v>
       </c>
       <c r="L25" t="n">
-        <v>0.208955223880597</v>
+        <v>0.2295081967213115</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3993993993993997</v>
+        <v>0.2753623188405798</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.462962962962963</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="D26" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="E26" t="n">
         <v>0.14</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.7777777777777779</v>
       </c>
       <c r="G26" t="n">
         <v>1.234567901234568</v>
@@ -1685,30 +1685,30 @@
         <v>0.02660000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>1.38</v>
+        <v>1.665000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2405063291139241</v>
+        <v>0.2317073170731708</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2295081967213115</v>
+        <v>0.208955223880597</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2753623188405798</v>
+        <v>0.3993993993993997</v>
       </c>
       <c r="N26" t="n">
-        <v>0.462962962962963</v>
+        <v>0.5000000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining'})</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1751,12 +1751,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1847,7 +1847,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1856,13 +1856,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
       <c r="D30" t="n">
         <v>0.51</v>
       </c>
       <c r="E30" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="F30" t="n">
         <v>0.625</v>
@@ -1874,28 +1874,28 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0276</v>
+        <v>0.0184</v>
       </c>
       <c r="J30" t="n">
         <v>1.306666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>0.2421052631578947</v>
+        <v>0.219047619047619</v>
       </c>
       <c r="L30" t="n">
-        <v>0.25</v>
+        <v>0.1754385964912281</v>
       </c>
       <c r="M30" t="n">
         <v>0.2346938775510204</v>
       </c>
       <c r="N30" t="n">
-        <v>0.4595588235294118</v>
+        <v>0.4105392156862745</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="D31" t="n">
         <v>0.51</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="F31" t="n">
         <v>0.625</v>
@@ -1922,33 +1922,33 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0184</v>
+        <v>0.0276</v>
       </c>
       <c r="J31" t="n">
         <v>1.306666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>0.219047619047619</v>
+        <v>0.2421052631578947</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1754385964912281</v>
+        <v>0.25</v>
       </c>
       <c r="M31" t="n">
         <v>0.2346938775510204</v>
       </c>
       <c r="N31" t="n">
-        <v>0.4105392156862745</v>
+        <v>0.4595588235294118</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining'})</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1991,7 +1991,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2039,22 +2039,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="D34" t="n">
         <v>0.55</v>
       </c>
       <c r="E34" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="F34" t="n">
         <v>0.6666666666666667</v>
@@ -2066,43 +2066,43 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.02450000000000001</v>
+        <v>0.0175</v>
       </c>
       <c r="J34" t="n">
         <v>1.35</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2215189873417722</v>
+        <v>0.2058823529411765</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M34" t="n">
         <v>0.2592592592592594</v>
       </c>
       <c r="N34" t="n">
-        <v>0.4606060606060607</v>
+        <v>0.4242424242424243</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="D35" t="n">
         <v>0.55</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="F35" t="n">
         <v>0.6666666666666667</v>
@@ -2114,28 +2114,28 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0175</v>
+        <v>0.02450000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>1.35</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2058823529411765</v>
+        <v>0.2215189873417722</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="M35" t="n">
         <v>0.2592592592592594</v>
       </c>
       <c r="N35" t="n">
-        <v>0.4242424242424243</v>
+        <v>0.4606060606060607</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Desain Grafis', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2183,7 +2183,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2192,13 +2192,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="D37" t="n">
         <v>0.62</v>
       </c>
       <c r="E37" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="F37" t="n">
         <v>0.75</v>
@@ -2210,28 +2210,28 @@
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0208</v>
+        <v>0.0416</v>
       </c>
       <c r="J37" t="n">
         <v>1.52</v>
       </c>
       <c r="K37" t="n">
-        <v>0.2063492063492064</v>
+        <v>0.2549019607843138</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="M37" t="n">
         <v>0.3421052631578947</v>
       </c>
       <c r="N37" t="n">
-        <v>0.4717741935483871</v>
+        <v>0.5685483870967742</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.32</v>
+        <v>0.16</v>
       </c>
       <c r="D38" t="n">
         <v>0.62</v>
       </c>
       <c r="E38" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="F38" t="n">
         <v>0.75</v>
@@ -2258,22 +2258,22 @@
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0416</v>
+        <v>0.0208</v>
       </c>
       <c r="J38" t="n">
         <v>1.52</v>
       </c>
       <c r="K38" t="n">
-        <v>0.2549019607843138</v>
+        <v>0.2063492063492064</v>
       </c>
       <c r="L38" t="n">
-        <v>0.3428571428571429</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="M38" t="n">
         <v>0.3421052631578947</v>
       </c>
       <c r="N38" t="n">
-        <v>0.5685483870967742</v>
+        <v>0.4717741935483871</v>
       </c>
     </row>
     <row r="39">
@@ -2327,7 +2327,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2375,7 +2375,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2423,7 +2423,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2471,7 +2471,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2567,22 +2567,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="D45" t="n">
         <v>0.57</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="F45" t="n">
         <v>0.6666666666666667</v>
@@ -2594,33 +2594,33 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>0.01450000000000001</v>
+        <v>0.02320000000000003</v>
       </c>
       <c r="J45" t="n">
         <v>1.29</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1705882352941178</v>
+        <v>0.1907894736842107</v>
       </c>
       <c r="L45" t="n">
-        <v>0.1612903225806452</v>
+        <v>0.2461538461538462</v>
       </c>
       <c r="M45" t="n">
         <v>0.2248062015503879</v>
       </c>
       <c r="N45" t="n">
-        <v>0.4210526315789474</v>
+        <v>0.4736842105263158</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2663,22 +2663,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="D47" t="n">
         <v>0.57</v>
       </c>
       <c r="E47" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="F47" t="n">
         <v>0.6666666666666667</v>
@@ -2690,28 +2690,28 @@
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0.02320000000000003</v>
+        <v>0.01450000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>1.29</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1907894736842107</v>
+        <v>0.1705882352941178</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2461538461538462</v>
+        <v>0.1612903225806452</v>
       </c>
       <c r="M47" t="n">
         <v>0.2248062015503879</v>
       </c>
       <c r="N47" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4210526315789474</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining'})</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -2855,7 +2855,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2903,7 +2903,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2951,7 +2951,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2960,13 +2960,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.21</v>
+        <v>0.14</v>
       </c>
       <c r="D53" t="n">
         <v>0.62</v>
       </c>
       <c r="E53" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="F53" t="n">
         <v>0.7142857142857143</v>
@@ -2978,28 +2978,28 @@
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.01980000000000001</v>
+        <v>0.0132</v>
       </c>
       <c r="J53" t="n">
         <v>1.33</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1670886075949368</v>
+        <v>0.1534883720930233</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2205882352941177</v>
+        <v>0.1515151515151515</v>
       </c>
       <c r="M53" t="n">
         <v>0.2481203007518797</v>
       </c>
       <c r="N53" t="n">
-        <v>0.478110599078341</v>
+        <v>0.4377880184331797</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining', 'Pemrograman CMS', 'Realitas Virtual'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3008,13 +3008,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="D54" t="n">
         <v>0.62</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="F54" t="n">
         <v>0.7142857142857143</v>
@@ -3026,28 +3026,28 @@
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0132</v>
+        <v>0.01980000000000001</v>
       </c>
       <c r="J54" t="n">
         <v>1.33</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1534883720930233</v>
+        <v>0.1670886075949368</v>
       </c>
       <c r="L54" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.2205882352941177</v>
       </c>
       <c r="M54" t="n">
         <v>0.2481203007518797</v>
       </c>
       <c r="N54" t="n">
-        <v>0.4377880184331797</v>
+        <v>0.478110599078341</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="D55" t="n">
         <v>0.87</v>
       </c>
       <c r="E55" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
@@ -3074,7 +3074,7 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0156</v>
+        <v>0.01949999999999999</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3082,22 +3082,22 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0.1477272727272728</v>
+        <v>0.1529411764705882</v>
       </c>
       <c r="L55" t="n">
-        <v>0.1379310344827586</v>
+        <v>0.1724137931034483</v>
       </c>
       <c r="M55" t="n">
         <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>0.5689655172413793</v>
+        <v>0.5862068965517241</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Data mining', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3106,13 +3106,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="D56" t="n">
         <v>0.87</v>
       </c>
       <c r="E56" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
@@ -3124,7 +3124,7 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>0.01949999999999999</v>
+        <v>0.0169</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3132,22 +3132,22 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>0.1529411764705882</v>
+        <v>0.1494252873563218</v>
       </c>
       <c r="L56" t="n">
-        <v>0.1724137931034483</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="M56" t="n">
         <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.5747126436781609</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Game Edukasi'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Game Edukasi', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3156,13 +3156,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="D57" t="n">
         <v>0.87</v>
       </c>
       <c r="E57" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -3174,7 +3174,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>0.02080000000000001</v>
+        <v>0.01949999999999999</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3182,22 +3182,22 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0.1547619047619049</v>
+        <v>0.1529411764705882</v>
       </c>
       <c r="L57" t="n">
-        <v>0.1839080459770115</v>
+        <v>0.1724137931034483</v>
       </c>
       <c r="M57" t="n">
         <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>0.5919540229885057</v>
+        <v>0.5862068965517241</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Data mining'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3206,13 +3206,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="D58" t="n">
         <v>0.87</v>
       </c>
       <c r="E58" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
@@ -3224,7 +3224,7 @@
         <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0169</v>
+        <v>0.02080000000000001</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3232,22 +3232,22 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0.1494252873563218</v>
+        <v>0.1547619047619049</v>
       </c>
       <c r="L58" t="n">
-        <v>0.1494252873563219</v>
+        <v>0.1839080459770115</v>
       </c>
       <c r="M58" t="n">
         <v>1</v>
       </c>
       <c r="N58" t="n">
-        <v>0.5747126436781609</v>
+        <v>0.5919540229885057</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Game Edukasi', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3256,13 +3256,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="D59" t="n">
         <v>0.87</v>
       </c>
       <c r="E59" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
@@ -3274,7 +3274,7 @@
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.01949999999999999</v>
+        <v>0.02080000000000001</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3282,22 +3282,22 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>0.1529411764705882</v>
+        <v>0.1547619047619049</v>
       </c>
       <c r="L59" t="n">
-        <v>0.1724137931034483</v>
+        <v>0.1839080459770115</v>
       </c>
       <c r="M59" t="n">
         <v>1</v>
       </c>
       <c r="N59" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.5919540229885057</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3397,7 +3397,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Data mining', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="D62" t="n">
         <v>0.87</v>
       </c>
       <c r="E62" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
@@ -3424,7 +3424,7 @@
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0.02080000000000001</v>
+        <v>0.0156</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3432,22 +3432,22 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>0.1547619047619049</v>
+        <v>0.1477272727272728</v>
       </c>
       <c r="L62" t="n">
-        <v>0.1839080459770115</v>
+        <v>0.1379310344827586</v>
       </c>
       <c r="M62" t="n">
         <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>0.5919540229885057</v>
+        <v>0.5689655172413793</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3495,12 +3495,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -3543,7 +3543,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Game Edukasi'})</t>
+          <t>frozenset({'Game Edukasi', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3639,7 +3639,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -3831,7 +3831,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3879,7 +3879,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Data mining'})</t>
+          <t>frozenset({'Data mining', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3975,7 +3975,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4071,25 +4071,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Teknologi IoT', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="D76" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="E76" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="F76" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="G76" t="n">
         <v>1.111111111111111</v>
@@ -4098,22 +4098,22 @@
         <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>0.012</v>
+        <v>0.02199999999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>1.2</v>
+        <v>1.157142857142857</v>
       </c>
       <c r="K76" t="n">
-        <v>0.1219512195121951</v>
+        <v>0.1562499999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.3188405797101449</v>
       </c>
       <c r="M76" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.1358024691358025</v>
       </c>
       <c r="N76" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.5055555555555555</v>
       </c>
     </row>
     <row r="77">
@@ -4167,25 +4167,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>frozenset({'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
+          <t>frozenset({'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.36</v>
+        <v>0.18</v>
       </c>
       <c r="D78" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="E78" t="n">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="F78" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G78" t="n">
         <v>1.111111111111111</v>
@@ -4194,46 +4194,46 @@
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.02199999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="J78" t="n">
-        <v>1.157142857142857</v>
+        <v>1.2</v>
       </c>
       <c r="K78" t="n">
-        <v>0.1562499999999999</v>
+        <v>0.1219512195121951</v>
       </c>
       <c r="L78" t="n">
-        <v>0.3188405797101449</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="M78" t="n">
-        <v>0.1358024691358025</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="N78" t="n">
-        <v>0.5055555555555555</v>
+        <v>0.4333333333333333</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining'})</t>
+          <t>frozenset({'Game Edukasi'})</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.31</v>
+        <v>0.16</v>
       </c>
       <c r="D79" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="E79" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="F79" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.6875</v>
       </c>
       <c r="G79" t="n">
         <v>1.108870967741935</v>
@@ -4242,28 +4242,28 @@
         <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>0.02160000000000001</v>
+        <v>0.0108</v>
       </c>
       <c r="J79" t="n">
-        <v>1.24</v>
+        <v>1.216</v>
       </c>
       <c r="K79" t="n">
-        <v>0.1422924901185771</v>
+        <v>0.1168831168831169</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3013698630136986</v>
+        <v>0.1641791044776119</v>
       </c>
       <c r="M79" t="n">
-        <v>0.1935483870967743</v>
+        <v>0.1776315789473684</v>
       </c>
       <c r="N79" t="n">
-        <v>0.5267137096774194</v>
+        <v>0.4324596774193549</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4311,25 +4311,25 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi'})</t>
+          <t>frozenset({'Data mining'})</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
       <c r="D81" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="E81" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="F81" t="n">
-        <v>0.6875</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="G81" t="n">
         <v>1.108870967741935</v>
@@ -4338,28 +4338,28 @@
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>0.0108</v>
+        <v>0.02160000000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>1.216</v>
+        <v>1.24</v>
       </c>
       <c r="K81" t="n">
-        <v>0.1168831168831169</v>
+        <v>0.1422924901185771</v>
       </c>
       <c r="L81" t="n">
-        <v>0.1641791044776119</v>
+        <v>0.3013698630136986</v>
       </c>
       <c r="M81" t="n">
-        <v>0.1776315789473684</v>
+        <v>0.1935483870967743</v>
       </c>
       <c r="N81" t="n">
-        <v>0.4324596774193549</v>
+        <v>0.5267137096774194</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4503,7 +4503,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4551,7 +4551,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4599,7 +4599,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4647,7 +4647,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4695,7 +4695,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4839,25 +4839,25 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>frozenset({'Data mining'})</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>frozenset({'Data mining'})</t>
-        </is>
-      </c>
       <c r="C92" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D92" t="n">
         <v>0.65</v>
-      </c>
-      <c r="D92" t="n">
-        <v>0.64</v>
       </c>
       <c r="E92" t="n">
         <v>0.45</v>
       </c>
       <c r="F92" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.703125</v>
       </c>
       <c r="G92" t="n">
         <v>1.081730769230769</v>
@@ -4869,16 +4869,16 @@
         <v>0.03399999999999997</v>
       </c>
       <c r="J92" t="n">
-        <v>1.17</v>
+        <v>1.178947368421053</v>
       </c>
       <c r="K92" t="n">
-        <v>0.2158730158730157</v>
+        <v>0.2098765432098764</v>
       </c>
       <c r="L92" t="n">
         <v>0.5357142857142857</v>
       </c>
       <c r="M92" t="n">
-        <v>0.1452991452991452</v>
+        <v>0.1517857142857142</v>
       </c>
       <c r="N92" t="n">
         <v>0.6977163461538461</v>
@@ -4887,25 +4887,25 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>frozenset({'Data mining'})</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
-        </is>
-      </c>
       <c r="C93" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D93" t="n">
         <v>0.64</v>
-      </c>
-      <c r="D93" t="n">
-        <v>0.65</v>
       </c>
       <c r="E93" t="n">
         <v>0.45</v>
       </c>
       <c r="F93" t="n">
-        <v>0.703125</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="G93" t="n">
         <v>1.081730769230769</v>
@@ -4917,16 +4917,16 @@
         <v>0.03399999999999997</v>
       </c>
       <c r="J93" t="n">
-        <v>1.178947368421053</v>
+        <v>1.17</v>
       </c>
       <c r="K93" t="n">
-        <v>0.2098765432098764</v>
+        <v>0.2158730158730157</v>
       </c>
       <c r="L93" t="n">
         <v>0.5357142857142857</v>
       </c>
       <c r="M93" t="n">
-        <v>0.1517857142857142</v>
+        <v>0.1452991452991452</v>
       </c>
       <c r="N93" t="n">
         <v>0.6977163461538461</v>
@@ -4935,7 +4935,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4983,7 +4983,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5127,7 +5127,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5175,7 +5175,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5223,7 +5223,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5367,7 +5367,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5463,7 +5463,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining'})</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5513,7 +5513,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining', 'Game Edukasi'})</t>
+          <t>frozenset({'Data mining', 'Game Edukasi', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5563,7 +5563,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5663,7 +5663,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5713,7 +5713,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5722,13 +5722,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.14</v>
+        <v>0.4</v>
       </c>
       <c r="D110" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E110" t="n">
-        <v>0.14</v>
+        <v>0.4</v>
       </c>
       <c r="F110" t="n">
         <v>1</v>
@@ -5740,7 +5740,7 @@
         <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>0.008400000000000019</v>
+        <v>0.02400000000000002</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -5748,22 +5748,22 @@
         </is>
       </c>
       <c r="K110" t="n">
-        <v>0.06976744186046527</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="L110" t="n">
-        <v>0.148936170212766</v>
+        <v>0.4255319148936171</v>
       </c>
       <c r="M110" t="n">
         <v>1</v>
       </c>
       <c r="N110" t="n">
-        <v>0.574468085106383</v>
+        <v>0.7127659574468086</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Desain Grafis', 'Data mining'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5772,13 +5772,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="D111" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E111" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="F111" t="n">
         <v>1</v>
@@ -5790,7 +5790,7 @@
         <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>0.007200000000000012</v>
+        <v>0.008400000000000019</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="K111" t="n">
-        <v>0.0681818181818183</v>
+        <v>0.06976744186046527</v>
       </c>
       <c r="L111" t="n">
-        <v>0.1276595744680851</v>
+        <v>0.148936170212766</v>
       </c>
       <c r="M111" t="n">
         <v>1</v>
       </c>
       <c r="N111" t="n">
-        <v>0.5638297872340425</v>
+        <v>0.574468085106383</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="D112" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E112" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
@@ -5840,7 +5840,7 @@
         <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>0.01440000000000002</v>
+        <v>0.007200000000000012</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -5848,22 +5848,22 @@
         </is>
       </c>
       <c r="K112" t="n">
-        <v>0.07894736842105277</v>
+        <v>0.0681818181818183</v>
       </c>
       <c r="L112" t="n">
-        <v>0.2553191489361702</v>
+        <v>0.1276595744680851</v>
       </c>
       <c r="M112" t="n">
         <v>1</v>
       </c>
       <c r="N112" t="n">
-        <v>0.6276595744680851</v>
+        <v>0.5638297872340425</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5872,13 +5872,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="D113" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E113" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="F113" t="n">
         <v>1</v>
@@ -5890,7 +5890,7 @@
         <v>1</v>
       </c>
       <c r="I113" t="n">
-        <v>0.009000000000000008</v>
+        <v>0.01440000000000002</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -5898,22 +5898,22 @@
         </is>
       </c>
       <c r="K113" t="n">
-        <v>0.0705882352941177</v>
+        <v>0.07894736842105277</v>
       </c>
       <c r="L113" t="n">
-        <v>0.1595744680851064</v>
+        <v>0.2553191489361702</v>
       </c>
       <c r="M113" t="n">
         <v>1</v>
       </c>
       <c r="N113" t="n">
-        <v>0.5797872340425532</v>
+        <v>0.6276595744680851</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5922,13 +5922,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="D114" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E114" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="F114" t="n">
         <v>1</v>
@@ -5940,7 +5940,7 @@
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>0.02400000000000002</v>
+        <v>0.009000000000000008</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -5948,22 +5948,22 @@
         </is>
       </c>
       <c r="K114" t="n">
-        <v>0.1000000000000001</v>
+        <v>0.0705882352941177</v>
       </c>
       <c r="L114" t="n">
-        <v>0.4255319148936171</v>
+        <v>0.1595744680851064</v>
       </c>
       <c r="M114" t="n">
         <v>1</v>
       </c>
       <c r="N114" t="n">
-        <v>0.7127659574468086</v>
+        <v>0.5797872340425532</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6013,7 +6013,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining'})</t>
+          <t>frozenset({'Data mining', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6063,7 +6063,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6113,7 +6113,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Realitas Virtual', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6122,13 +6122,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="D118" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E118" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
@@ -6140,7 +6140,7 @@
         <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.01320000000000002</v>
+        <v>0.006000000000000005</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -6148,22 +6148,22 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>0.07692307692307702</v>
+        <v>0.06666666666666672</v>
       </c>
       <c r="L118" t="n">
-        <v>0.2340425531914894</v>
+        <v>0.1063829787234043</v>
       </c>
       <c r="M118" t="n">
         <v>1</v>
       </c>
       <c r="N118" t="n">
-        <v>0.6170212765957447</v>
+        <v>0.5531914893617021</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining', 'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Sistem Informasi Pendidikan'})</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6213,7 +6213,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6222,13 +6222,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="D120" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E120" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="F120" t="n">
         <v>1</v>
@@ -6240,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>0.008400000000000019</v>
+        <v>0.009599999999999997</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -6248,22 +6248,22 @@
         </is>
       </c>
       <c r="K120" t="n">
-        <v>0.06976744186046527</v>
+        <v>0.07142857142857141</v>
       </c>
       <c r="L120" t="n">
-        <v>0.148936170212766</v>
+        <v>0.1702127659574468</v>
       </c>
       <c r="M120" t="n">
         <v>1</v>
       </c>
       <c r="N120" t="n">
-        <v>0.574468085106383</v>
+        <v>0.5851063829787234</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6272,13 +6272,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="D121" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E121" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
@@ -6290,7 +6290,7 @@
         <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>0.009599999999999997</v>
+        <v>0.008400000000000019</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -6298,22 +6298,22 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>0.07142857142857141</v>
+        <v>0.06976744186046527</v>
       </c>
       <c r="L121" t="n">
-        <v>0.1702127659574468</v>
+        <v>0.148936170212766</v>
       </c>
       <c r="M121" t="n">
         <v>1</v>
       </c>
       <c r="N121" t="n">
-        <v>0.5851063829787234</v>
+        <v>0.574468085106383</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6322,13 +6322,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="D122" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E122" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="F122" t="n">
         <v>1</v>
@@ -6340,7 +6340,7 @@
         <v>1</v>
       </c>
       <c r="I122" t="n">
-        <v>0.01140000000000002</v>
+        <v>0.01320000000000002</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -6348,22 +6348,22 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>0.07407407407407421</v>
+        <v>0.07692307692307702</v>
       </c>
       <c r="L122" t="n">
-        <v>0.2021276595744681</v>
+        <v>0.2340425531914894</v>
       </c>
       <c r="M122" t="n">
         <v>1</v>
       </c>
       <c r="N122" t="n">
-        <v>0.601063829787234</v>
+        <v>0.6170212765957447</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Informasi Pendidikan'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6372,13 +6372,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="D123" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E123" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -6390,7 +6390,7 @@
         <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>0.006000000000000005</v>
+        <v>0.01140000000000002</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -6398,22 +6398,22 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>0.06666666666666672</v>
+        <v>0.07407407407407421</v>
       </c>
       <c r="L123" t="n">
-        <v>0.1063829787234043</v>
+        <v>0.2021276595744681</v>
       </c>
       <c r="M123" t="n">
         <v>1</v>
       </c>
       <c r="N123" t="n">
-        <v>0.5531914893617021</v>
+        <v>0.601063829787234</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -6461,12 +6461,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -6509,7 +6509,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -6557,7 +6557,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining'})</t>
+          <t>frozenset({'Data mining', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6605,7 +6605,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6653,7 +6653,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6749,7 +6749,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>frozenset({'Teknologi IoT', 'Pemrograman CMS', 'Data mining', 'Game Edukasi', 'Realitas Virtual'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6758,13 +6758,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="D131" t="n">
         <v>0.68</v>
       </c>
       <c r="E131" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="F131" t="n">
         <v>0.7142857142857143</v>
@@ -6776,46 +6776,46 @@
         <v>1</v>
       </c>
       <c r="I131" t="n">
-        <v>0.004799999999999985</v>
+        <v>0.007199999999999984</v>
       </c>
       <c r="J131" t="n">
         <v>1.12</v>
       </c>
       <c r="K131" t="n">
-        <v>0.05581395348837191</v>
+        <v>0.06075949367088595</v>
       </c>
       <c r="L131" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.2027027027027027</v>
       </c>
       <c r="M131" t="n">
         <v>0.1071428571428571</v>
       </c>
       <c r="N131" t="n">
-        <v>0.430672268907563</v>
+        <v>0.467436974789916</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0.14</v>
+        <v>0.68</v>
       </c>
       <c r="D132" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="E132" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="F132" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6617647058823529</v>
       </c>
       <c r="G132" t="n">
         <v>1.050420168067227</v>
@@ -6824,28 +6824,28 @@
         <v>1</v>
       </c>
       <c r="I132" t="n">
-        <v>0.004799999999999985</v>
+        <v>0.02159999999999995</v>
       </c>
       <c r="J132" t="n">
-        <v>1.12</v>
+        <v>1.093913043478261</v>
       </c>
       <c r="K132" t="n">
-        <v>0.05581395348837191</v>
+        <v>0.1499999999999997</v>
       </c>
       <c r="L132" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.5232558139534883</v>
       </c>
       <c r="M132" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.08585055643879166</v>
       </c>
       <c r="N132" t="n">
-        <v>0.430672268907563</v>
+        <v>0.6880252100840336</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Data mining', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6854,13 +6854,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0.21</v>
+        <v>0.14</v>
       </c>
       <c r="D133" t="n">
         <v>0.68</v>
       </c>
       <c r="E133" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="F133" t="n">
         <v>0.7142857142857143</v>
@@ -6872,22 +6872,22 @@
         <v>1</v>
       </c>
       <c r="I133" t="n">
-        <v>0.007199999999999984</v>
+        <v>0.004799999999999985</v>
       </c>
       <c r="J133" t="n">
         <v>1.12</v>
       </c>
       <c r="K133" t="n">
-        <v>0.06075949367088595</v>
+        <v>0.05581395348837191</v>
       </c>
       <c r="L133" t="n">
-        <v>0.2027027027027027</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="M133" t="n">
         <v>0.1071428571428571</v>
       </c>
       <c r="N133" t="n">
-        <v>0.467436974789916</v>
+        <v>0.430672268907563</v>
       </c>
     </row>
     <row r="134">
@@ -6941,25 +6941,25 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Data mining', 'Game Edukasi'})</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
           <t>frozenset({'Pengolahan Citra Digital'})</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
-        </is>
-      </c>
       <c r="C135" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D135" t="n">
         <v>0.68</v>
       </c>
-      <c r="D135" t="n">
-        <v>0.63</v>
-      </c>
       <c r="E135" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="F135" t="n">
-        <v>0.6617647058823529</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="G135" t="n">
         <v>1.050420168067227</v>
@@ -6968,28 +6968,28 @@
         <v>1</v>
       </c>
       <c r="I135" t="n">
-        <v>0.02159999999999995</v>
+        <v>0.004799999999999985</v>
       </c>
       <c r="J135" t="n">
-        <v>1.093913043478261</v>
+        <v>1.12</v>
       </c>
       <c r="K135" t="n">
-        <v>0.1499999999999997</v>
+        <v>0.05581395348837191</v>
       </c>
       <c r="L135" t="n">
-        <v>0.5232558139534883</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="M135" t="n">
-        <v>0.08585055643879166</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="N135" t="n">
-        <v>0.6880252100840336</v>
+        <v>0.430672268907563</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7133,7 +7133,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS', 'Data mining', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7181,7 +7181,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7229,7 +7229,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7277,25 +7277,25 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
           <t>frozenset({'Pemrograman CMS'})</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
-        </is>
-      </c>
       <c r="C142" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D142" t="n">
         <v>0.9399999999999999</v>
-      </c>
-      <c r="D142" t="n">
-        <v>0.55</v>
       </c>
       <c r="E142" t="n">
         <v>0.54</v>
       </c>
       <c r="F142" t="n">
-        <v>0.574468085106383</v>
+        <v>0.9818181818181818</v>
       </c>
       <c r="G142" t="n">
         <v>1.044487427466151</v>
@@ -7307,16 +7307,16 @@
         <v>0.02300000000000002</v>
       </c>
       <c r="J142" t="n">
-        <v>1.0575</v>
+        <v>3.300000000000002</v>
       </c>
       <c r="K142" t="n">
-        <v>0.7098765432098765</v>
+        <v>0.09465020576131696</v>
       </c>
       <c r="L142" t="n">
         <v>0.568421052631579</v>
       </c>
       <c r="M142" t="n">
-        <v>0.05437352245862886</v>
+        <v>0.6969696969696971</v>
       </c>
       <c r="N142" t="n">
         <v>0.7781431334622824</v>
@@ -7325,25 +7325,25 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
+          <t>frozenset({'Pemrograman CMS'})</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
           <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>frozenset({'Pemrograman CMS'})</t>
-        </is>
-      </c>
       <c r="C143" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D143" t="n">
         <v>0.55</v>
-      </c>
-      <c r="D143" t="n">
-        <v>0.9399999999999999</v>
       </c>
       <c r="E143" t="n">
         <v>0.54</v>
       </c>
       <c r="F143" t="n">
-        <v>0.9818181818181818</v>
+        <v>0.574468085106383</v>
       </c>
       <c r="G143" t="n">
         <v>1.044487427466151</v>
@@ -7355,16 +7355,16 @@
         <v>0.02300000000000002</v>
       </c>
       <c r="J143" t="n">
-        <v>3.300000000000002</v>
+        <v>1.0575</v>
       </c>
       <c r="K143" t="n">
-        <v>0.09465020576131696</v>
+        <v>0.7098765432098765</v>
       </c>
       <c r="L143" t="n">
         <v>0.568421052631579</v>
       </c>
       <c r="M143" t="n">
-        <v>0.6969696969696971</v>
+        <v>0.05437352245862886</v>
       </c>
       <c r="N143" t="n">
         <v>0.7781431334622824</v>
@@ -7565,7 +7565,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7613,7 +7613,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7709,7 +7709,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -7853,25 +7853,25 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>frozenset({'Pengolahan Citra Digital'})</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
           <t>frozenset({'Data mining'})</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>frozenset({'Pengolahan Citra Digital'})</t>
-        </is>
-      </c>
       <c r="C154" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D154" t="n">
         <v>0.64</v>
-      </c>
-      <c r="D154" t="n">
-        <v>0.68</v>
       </c>
       <c r="E154" t="n">
         <v>0.45</v>
       </c>
       <c r="F154" t="n">
-        <v>0.703125</v>
+        <v>0.6617647058823529</v>
       </c>
       <c r="G154" t="n">
         <v>1.034007352941176</v>
@@ -7883,16 +7883,16 @@
         <v>0.01479999999999998</v>
       </c>
       <c r="J154" t="n">
-        <v>1.077894736842105</v>
+        <v>1.064347826086956</v>
       </c>
       <c r="K154" t="n">
-        <v>0.0913580246913579</v>
+        <v>0.1027777777777776</v>
       </c>
       <c r="L154" t="n">
         <v>0.5172413793103448</v>
       </c>
       <c r="M154" t="n">
-        <v>0.07226562499999986</v>
+        <v>0.06045751633986919</v>
       </c>
       <c r="N154" t="n">
         <v>0.6824448529411764</v>
@@ -7901,25 +7901,25 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
+          <t>frozenset({'Data mining'})</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
           <t>frozenset({'Pengolahan Citra Digital'})</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>frozenset({'Data mining'})</t>
-        </is>
-      </c>
       <c r="C155" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D155" t="n">
         <v>0.68</v>
-      </c>
-      <c r="D155" t="n">
-        <v>0.64</v>
       </c>
       <c r="E155" t="n">
         <v>0.45</v>
       </c>
       <c r="F155" t="n">
-        <v>0.6617647058823529</v>
+        <v>0.703125</v>
       </c>
       <c r="G155" t="n">
         <v>1.034007352941176</v>
@@ -7931,16 +7931,16 @@
         <v>0.01479999999999998</v>
       </c>
       <c r="J155" t="n">
-        <v>1.064347826086956</v>
+        <v>1.077894736842105</v>
       </c>
       <c r="K155" t="n">
-        <v>0.1027777777777776</v>
+        <v>0.0913580246913579</v>
       </c>
       <c r="L155" t="n">
         <v>0.5172413793103448</v>
       </c>
       <c r="M155" t="n">
-        <v>0.06045751633986919</v>
+        <v>0.07226562499999986</v>
       </c>
       <c r="N155" t="n">
         <v>0.6824448529411764</v>
@@ -8045,25 +8045,25 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
+          <t>frozenset({'Data mining'})</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
           <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>frozenset({'Data mining'})</t>
-        </is>
-      </c>
       <c r="C158" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D158" t="n">
         <v>0.82</v>
-      </c>
-      <c r="D158" t="n">
-        <v>0.64</v>
       </c>
       <c r="E158" t="n">
         <v>0.54</v>
       </c>
       <c r="F158" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.84375</v>
       </c>
       <c r="G158" t="n">
         <v>1.028963414634146</v>
@@ -8075,16 +8075,16 @@
         <v>0.0152000000000001</v>
       </c>
       <c r="J158" t="n">
-        <v>1.054285714285714</v>
+        <v>1.152</v>
       </c>
       <c r="K158" t="n">
-        <v>0.1563786008230462</v>
+        <v>0.07818930041152315</v>
       </c>
       <c r="L158" t="n">
         <v>0.5869565217391305</v>
       </c>
       <c r="M158" t="n">
-        <v>0.0514905149051491</v>
+        <v>0.1319444444444447</v>
       </c>
       <c r="N158" t="n">
         <v>0.7511432926829269</v>
@@ -8093,25 +8093,25 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
           <t>frozenset({'Data mining'})</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
-        </is>
-      </c>
       <c r="C159" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D159" t="n">
         <v>0.64</v>
-      </c>
-      <c r="D159" t="n">
-        <v>0.82</v>
       </c>
       <c r="E159" t="n">
         <v>0.54</v>
       </c>
       <c r="F159" t="n">
-        <v>0.84375</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="G159" t="n">
         <v>1.028963414634146</v>
@@ -8123,16 +8123,16 @@
         <v>0.0152000000000001</v>
       </c>
       <c r="J159" t="n">
-        <v>1.152</v>
+        <v>1.054285714285714</v>
       </c>
       <c r="K159" t="n">
-        <v>0.07818930041152315</v>
+        <v>0.1563786008230462</v>
       </c>
       <c r="L159" t="n">
         <v>0.5869565217391305</v>
       </c>
       <c r="M159" t="n">
-        <v>0.1319444444444447</v>
+        <v>0.0514905149051491</v>
       </c>
       <c r="N159" t="n">
         <v>0.7511432926829269</v>
@@ -8141,7 +8141,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -8237,7 +8237,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -8285,7 +8285,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -8333,7 +8333,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -8381,7 +8381,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -8429,25 +8429,25 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
+          <t>frozenset({'Game Edukasi'})</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
           <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>frozenset({'Game Edukasi'})</t>
-        </is>
-      </c>
       <c r="C166" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D166" t="n">
         <v>0.63</v>
-      </c>
-      <c r="D166" t="n">
-        <v>0.62</v>
       </c>
       <c r="E166" t="n">
         <v>0.4</v>
       </c>
       <c r="F166" t="n">
-        <v>0.634920634920635</v>
+        <v>0.6451612903225807</v>
       </c>
       <c r="G166" t="n">
         <v>1.024065540194573</v>
@@ -8459,16 +8459,16 @@
         <v>0.009400000000000019</v>
       </c>
       <c r="J166" t="n">
-        <v>1.040869565217392</v>
+        <v>1.042727272727273</v>
       </c>
       <c r="K166" t="n">
-        <v>0.06351351351351364</v>
+        <v>0.06184210526315801</v>
       </c>
       <c r="L166" t="n">
         <v>0.4705882352941177</v>
       </c>
       <c r="M166" t="n">
-        <v>0.03926482873851316</v>
+        <v>0.04097646033129928</v>
       </c>
       <c r="N166" t="n">
         <v>0.6400409626216079</v>
@@ -8477,25 +8477,25 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
+          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
           <t>frozenset({'Game Edukasi'})</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
-        </is>
-      </c>
       <c r="C167" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D167" t="n">
         <v>0.62</v>
-      </c>
-      <c r="D167" t="n">
-        <v>0.63</v>
       </c>
       <c r="E167" t="n">
         <v>0.4</v>
       </c>
       <c r="F167" t="n">
-        <v>0.6451612903225807</v>
+        <v>0.634920634920635</v>
       </c>
       <c r="G167" t="n">
         <v>1.024065540194573</v>
@@ -8507,16 +8507,16 @@
         <v>0.009400000000000019</v>
       </c>
       <c r="J167" t="n">
-        <v>1.042727272727273</v>
+        <v>1.040869565217392</v>
       </c>
       <c r="K167" t="n">
-        <v>0.06184210526315801</v>
+        <v>0.06351351351351364</v>
       </c>
       <c r="L167" t="n">
         <v>0.4705882352941177</v>
       </c>
       <c r="M167" t="n">
-        <v>0.04097646033129928</v>
+        <v>0.03926482873851316</v>
       </c>
       <c r="N167" t="n">
         <v>0.6400409626216079</v>
@@ -8525,7 +8525,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -8669,12 +8669,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -8717,12 +8717,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -8813,7 +8813,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -8861,7 +8861,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Game Edukasi'})</t>
+          <t>frozenset({'Game Edukasi', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -9245,25 +9245,25 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
+          <t>frozenset({'Data mining'})</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
           <t>frozenset({'Realitas Virtual', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>frozenset({'Data mining'})</t>
-        </is>
-      </c>
       <c r="C183" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D183" t="n">
         <v>0.51</v>
-      </c>
-      <c r="D183" t="n">
-        <v>0.64</v>
       </c>
       <c r="E183" t="n">
         <v>0.33</v>
       </c>
       <c r="F183" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.515625</v>
       </c>
       <c r="G183" t="n">
         <v>1.011029411764706</v>
@@ -9275,16 +9275,16 @@
         <v>0.003599999999999992</v>
       </c>
       <c r="J183" t="n">
-        <v>1.02</v>
+        <v>1.011612903225806</v>
       </c>
       <c r="K183" t="n">
-        <v>0.02226345083487936</v>
+        <v>0.03030303030303023</v>
       </c>
       <c r="L183" t="n">
         <v>0.402439024390244</v>
       </c>
       <c r="M183" t="n">
-        <v>0.01960784313725496</v>
+        <v>0.01147959183673468</v>
       </c>
       <c r="N183" t="n">
         <v>0.5813419117647058</v>
@@ -9293,25 +9293,25 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining'})</t>
+          <t>frozenset({'Data mining', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Game Edukasi', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital'})</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0.64</v>
+        <v>0.16</v>
       </c>
       <c r="D184" t="n">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
       <c r="E184" t="n">
-        <v>0.33</v>
+        <v>0.11</v>
       </c>
       <c r="F184" t="n">
-        <v>0.515625</v>
+        <v>0.6875</v>
       </c>
       <c r="G184" t="n">
         <v>1.011029411764706</v>
@@ -9320,28 +9320,28 @@
         <v>1</v>
       </c>
       <c r="I184" t="n">
-        <v>0.003599999999999992</v>
+        <v>0.001199999999999993</v>
       </c>
       <c r="J184" t="n">
-        <v>1.011612903225806</v>
+        <v>1.024</v>
       </c>
       <c r="K184" t="n">
-        <v>0.03030303030303023</v>
+        <v>0.01298701298701291</v>
       </c>
       <c r="L184" t="n">
-        <v>0.402439024390244</v>
+        <v>0.1506849315068493</v>
       </c>
       <c r="M184" t="n">
-        <v>0.01147959183673468</v>
+        <v>0.02343749999999985</v>
       </c>
       <c r="N184" t="n">
-        <v>0.5813419117647058</v>
+        <v>0.4246323529411765</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Data mining', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -9389,25 +9389,25 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Data mining'})</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>0.16</v>
+        <v>0.51</v>
       </c>
       <c r="D186" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="E186" t="n">
-        <v>0.11</v>
+        <v>0.33</v>
       </c>
       <c r="F186" t="n">
-        <v>0.6875</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="G186" t="n">
         <v>1.011029411764706</v>
@@ -9416,28 +9416,28 @@
         <v>1</v>
       </c>
       <c r="I186" t="n">
-        <v>0.001199999999999993</v>
+        <v>0.003599999999999992</v>
       </c>
       <c r="J186" t="n">
-        <v>1.024</v>
+        <v>1.02</v>
       </c>
       <c r="K186" t="n">
-        <v>0.01298701298701291</v>
+        <v>0.02226345083487936</v>
       </c>
       <c r="L186" t="n">
-        <v>0.1506849315068493</v>
+        <v>0.402439024390244</v>
       </c>
       <c r="M186" t="n">
-        <v>0.02343749999999985</v>
+        <v>0.01960784313725496</v>
       </c>
       <c r="N186" t="n">
-        <v>0.4246323529411765</v>
+        <v>0.5813419117647058</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -9533,7 +9533,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -9581,7 +9581,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining'})</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -9590,13 +9590,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>0.24</v>
+        <v>0.64</v>
       </c>
       <c r="D190" t="n">
         <v>0.62</v>
       </c>
       <c r="E190" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="F190" t="n">
         <v>0.625</v>
@@ -9608,28 +9608,28 @@
         <v>1</v>
       </c>
       <c r="I190" t="n">
-        <v>0.001200000000000007</v>
+        <v>0.003200000000000036</v>
       </c>
       <c r="J190" t="n">
         <v>1.013333333333333</v>
       </c>
       <c r="K190" t="n">
-        <v>0.01052631578947374</v>
+        <v>0.02222222222222248</v>
       </c>
       <c r="L190" t="n">
-        <v>0.2112676056338028</v>
+        <v>0.4651162790697675</v>
       </c>
       <c r="M190" t="n">
         <v>0.01315789473684212</v>
       </c>
       <c r="N190" t="n">
-        <v>0.4334677419354839</v>
+        <v>0.6350806451612904</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -9638,13 +9638,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>0.64</v>
+        <v>0.24</v>
       </c>
       <c r="D191" t="n">
         <v>0.62</v>
       </c>
       <c r="E191" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="F191" t="n">
         <v>0.625</v>
@@ -9656,28 +9656,28 @@
         <v>1</v>
       </c>
       <c r="I191" t="n">
-        <v>0.003200000000000036</v>
+        <v>0.001200000000000007</v>
       </c>
       <c r="J191" t="n">
         <v>1.013333333333333</v>
       </c>
       <c r="K191" t="n">
-        <v>0.02222222222222248</v>
+        <v>0.01052631578947374</v>
       </c>
       <c r="L191" t="n">
-        <v>0.4651162790697675</v>
+        <v>0.2112676056338028</v>
       </c>
       <c r="M191" t="n">
         <v>0.01315789473684212</v>
       </c>
       <c r="N191" t="n">
-        <v>0.6350806451612904</v>
+        <v>0.4334677419354839</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Desain Grafis', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -9686,13 +9686,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
       <c r="D192" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E192" t="n">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="F192" t="n">
         <v>0.9473684210526315</v>
@@ -9704,28 +9704,28 @@
         <v>1</v>
       </c>
       <c r="I192" t="n">
-        <v>0.001400000000000012</v>
+        <v>0.002800000000000025</v>
       </c>
       <c r="J192" t="n">
         <v>1.14</v>
       </c>
       <c r="K192" t="n">
-        <v>0.009602194787380057</v>
+        <v>0.01254480286738362</v>
       </c>
       <c r="L192" t="n">
-        <v>0.1894736842105263</v>
+        <v>0.3750000000000001</v>
       </c>
       <c r="M192" t="n">
         <v>0.1228070175438595</v>
       </c>
       <c r="N192" t="n">
-        <v>0.5694288913773796</v>
+        <v>0.6651735722284434</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>frozenset({'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -9734,13 +9734,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
       <c r="D193" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E193" t="n">
-        <v>0.36</v>
+        <v>0.18</v>
       </c>
       <c r="F193" t="n">
         <v>0.9473684210526315</v>
@@ -9752,46 +9752,46 @@
         <v>1</v>
       </c>
       <c r="I193" t="n">
-        <v>0.002800000000000025</v>
+        <v>0.001400000000000012</v>
       </c>
       <c r="J193" t="n">
         <v>1.14</v>
       </c>
       <c r="K193" t="n">
-        <v>0.01254480286738362</v>
+        <v>0.009602194787380057</v>
       </c>
       <c r="L193" t="n">
-        <v>0.3750000000000001</v>
+        <v>0.1894736842105263</v>
       </c>
       <c r="M193" t="n">
         <v>0.1228070175438595</v>
       </c>
       <c r="N193" t="n">
-        <v>0.6651735722284434</v>
+        <v>0.5694288913773796</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
           <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
-        </is>
-      </c>
       <c r="C194" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D194" t="n">
         <v>0.65</v>
-      </c>
-      <c r="D194" t="n">
-        <v>0.55</v>
       </c>
       <c r="E194" t="n">
         <v>0.36</v>
       </c>
       <c r="F194" t="n">
-        <v>0.5538461538461538</v>
+        <v>0.6545454545454544</v>
       </c>
       <c r="G194" t="n">
         <v>1.006993006993007</v>
@@ -9803,16 +9803,16 @@
         <v>0.002499999999999947</v>
       </c>
       <c r="J194" t="n">
-        <v>1.008620689655172</v>
+        <v>1.013157894736842</v>
       </c>
       <c r="K194" t="n">
-        <v>0.01984126984126942</v>
+        <v>0.01543209876543177</v>
       </c>
       <c r="L194" t="n">
         <v>0.4285714285714284</v>
       </c>
       <c r="M194" t="n">
-        <v>0.00854700854700827</v>
+        <v>0.0129870129870126</v>
       </c>
       <c r="N194" t="n">
         <v>0.6041958041958041</v>
@@ -9821,25 +9821,25 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
+          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
           <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
-        </is>
-      </c>
       <c r="C195" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D195" t="n">
         <v>0.55</v>
-      </c>
-      <c r="D195" t="n">
-        <v>0.65</v>
       </c>
       <c r="E195" t="n">
         <v>0.36</v>
       </c>
       <c r="F195" t="n">
-        <v>0.6545454545454544</v>
+        <v>0.5538461538461538</v>
       </c>
       <c r="G195" t="n">
         <v>1.006993006993007</v>
@@ -9851,16 +9851,16 @@
         <v>0.002499999999999947</v>
       </c>
       <c r="J195" t="n">
-        <v>1.013157894736842</v>
+        <v>1.008620689655172</v>
       </c>
       <c r="K195" t="n">
-        <v>0.01543209876543177</v>
+        <v>0.01984126984126942</v>
       </c>
       <c r="L195" t="n">
         <v>0.4285714285714284</v>
       </c>
       <c r="M195" t="n">
-        <v>0.0129870129870126</v>
+        <v>0.00854700854700827</v>
       </c>
       <c r="N195" t="n">
         <v>0.6041958041958041</v>
@@ -9917,7 +9917,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -9965,7 +9965,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -10013,7 +10013,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -10061,7 +10061,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -10109,25 +10109,25 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
           <t>frozenset({'Game Edukasi'})</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
-        </is>
-      </c>
       <c r="C201" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D201" t="n">
         <v>0.62</v>
-      </c>
-      <c r="D201" t="n">
-        <v>0.82</v>
       </c>
       <c r="E201" t="n">
         <v>0.51</v>
       </c>
       <c r="F201" t="n">
-        <v>0.8225806451612904</v>
+        <v>0.6219512195121951</v>
       </c>
       <c r="G201" t="n">
         <v>1.003147128245476</v>
@@ -10139,16 +10139,16 @@
         <v>0.001600000000000046</v>
       </c>
       <c r="J201" t="n">
-        <v>1.014545454545455</v>
+        <v>1.005161290322581</v>
       </c>
       <c r="K201" t="n">
-        <v>0.008255933952528617</v>
+        <v>0.01742919389978263</v>
       </c>
       <c r="L201" t="n">
         <v>0.5483870967741936</v>
       </c>
       <c r="M201" t="n">
-        <v>0.01433691756272454</v>
+        <v>0.005134788189987168</v>
       </c>
       <c r="N201" t="n">
         <v>0.7222659323367427</v>
@@ -10157,25 +10157,25 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
+          <t>frozenset({'Game Edukasi'})</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
           <t>frozenset({'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>frozenset({'Game Edukasi'})</t>
-        </is>
-      </c>
       <c r="C202" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D202" t="n">
         <v>0.82</v>
-      </c>
-      <c r="D202" t="n">
-        <v>0.62</v>
       </c>
       <c r="E202" t="n">
         <v>0.51</v>
       </c>
       <c r="F202" t="n">
-        <v>0.6219512195121951</v>
+        <v>0.8225806451612904</v>
       </c>
       <c r="G202" t="n">
         <v>1.003147128245476</v>
@@ -10187,16 +10187,16 @@
         <v>0.001600000000000046</v>
       </c>
       <c r="J202" t="n">
-        <v>1.005161290322581</v>
+        <v>1.014545454545455</v>
       </c>
       <c r="K202" t="n">
-        <v>0.01742919389978263</v>
+        <v>0.008255933952528617</v>
       </c>
       <c r="L202" t="n">
         <v>0.5483870967741936</v>
       </c>
       <c r="M202" t="n">
-        <v>0.005134788189987168</v>
+        <v>0.01433691756272454</v>
       </c>
       <c r="N202" t="n">
         <v>0.7222659323367427</v>
@@ -10301,7 +10301,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -10349,25 +10349,25 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>frozenset({'Teknologi IoT'})</t>
+          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>0.38</v>
+        <v>0.63</v>
       </c>
       <c r="D206" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="E206" t="n">
-        <v>0.24</v>
+        <v>0.36</v>
       </c>
       <c r="F206" t="n">
-        <v>0.631578947368421</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="G206" t="n">
         <v>1.00250626566416</v>
@@ -10376,46 +10376,46 @@
         <v>1</v>
       </c>
       <c r="I206" t="n">
-        <v>0.0005999999999999894</v>
+        <v>0.0009000000000000119</v>
       </c>
       <c r="J206" t="n">
-        <v>1.004285714285714</v>
+        <v>1.003333333333333</v>
       </c>
       <c r="K206" t="n">
-        <v>0.004032258064516059</v>
+        <v>0.006756756756756846</v>
       </c>
       <c r="L206" t="n">
-        <v>0.3116883116883117</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="M206" t="n">
-        <v>0.004267425320056792</v>
+        <v>0.003322259136212664</v>
       </c>
       <c r="N206" t="n">
-        <v>0.506265664160401</v>
+        <v>0.6015037593984962</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
+          <t>frozenset({'Teknologi IoT'})</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
           <t>frozenset({'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
-        </is>
-      </c>
       <c r="C207" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D207" t="n">
         <v>0.63</v>
       </c>
-      <c r="D207" t="n">
-        <v>0.57</v>
-      </c>
       <c r="E207" t="n">
-        <v>0.36</v>
+        <v>0.24</v>
       </c>
       <c r="F207" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="G207" t="n">
         <v>1.00250626566416</v>
@@ -10424,22 +10424,22 @@
         <v>1</v>
       </c>
       <c r="I207" t="n">
-        <v>0.0009000000000000119</v>
+        <v>0.0005999999999999894</v>
       </c>
       <c r="J207" t="n">
-        <v>1.003333333333333</v>
+        <v>1.004285714285714</v>
       </c>
       <c r="K207" t="n">
-        <v>0.006756756756756846</v>
+        <v>0.004032258064516059</v>
       </c>
       <c r="L207" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.3116883116883117</v>
       </c>
       <c r="M207" t="n">
-        <v>0.003322259136212664</v>
+        <v>0.004267425320056792</v>
       </c>
       <c r="N207" t="n">
-        <v>0.6015037593984962</v>
+        <v>0.506265664160401</v>
       </c>
     </row>
     <row r="208">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -10541,25 +10541,25 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
+          <t>frozenset({'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="D210" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="E210" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="F210" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="G210" t="n">
         <v>1</v>
@@ -10577,37 +10577,37 @@
         <v>0</v>
       </c>
       <c r="L210" t="n">
-        <v>0.402439024390244</v>
+        <v>0.3291139240506329</v>
       </c>
       <c r="M210" t="n">
         <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>0.575</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Data mining'})</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="D211" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="E211" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="F211" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="G211" t="n">
         <v>1</v>
@@ -10625,37 +10625,37 @@
         <v>0</v>
       </c>
       <c r="L211" t="n">
-        <v>0.3291139240506329</v>
+        <v>0.2191780821917808</v>
       </c>
       <c r="M211" t="n">
         <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>0.525</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining'})</t>
+          <t>frozenset({'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>0.25</v>
+        <v>0.55</v>
       </c>
       <c r="D212" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="E212" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="F212" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="G212" t="n">
         <v>1</v>
@@ -10673,13 +10673,13 @@
         <v>0</v>
       </c>
       <c r="L212" t="n">
-        <v>0.2191780821917808</v>
+        <v>0.402439024390244</v>
       </c>
       <c r="M212" t="n">
         <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>0.445</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="213">
@@ -10733,7 +10733,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -10829,7 +10829,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -10877,7 +10877,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Game Edukasi', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -10925,7 +10925,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -10973,7 +10973,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan', 'Game Edukasi'})</t>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -11069,7 +11069,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -11165,7 +11165,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -11501,25 +11501,25 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Data mining'})</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="C230" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D230" t="n">
         <v>0.57</v>
-      </c>
-      <c r="D230" t="n">
-        <v>0.64</v>
       </c>
       <c r="E230" t="n">
         <v>0.36</v>
       </c>
       <c r="F230" t="n">
-        <v>0.6315789473684211</v>
+        <v>0.5625</v>
       </c>
       <c r="G230" t="n">
         <v>0.986842105263158</v>
@@ -11531,16 +11531,16 @@
         <v>-0.004799999999999971</v>
       </c>
       <c r="J230" t="n">
-        <v>0.9771428571428573</v>
+        <v>0.982857142857143</v>
       </c>
       <c r="K230" t="n">
-        <v>-0.03007518796992463</v>
+        <v>-0.0357142857142855</v>
       </c>
       <c r="L230" t="n">
         <v>0.4235294117647059</v>
       </c>
       <c r="M230" t="n">
-        <v>-0.0233918128654969</v>
+        <v>-0.01744186046511616</v>
       </c>
       <c r="N230" t="n">
         <v>0.5970394736842106</v>
@@ -11549,25 +11549,25 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
           <t>frozenset({'Data mining'})</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
-        </is>
-      </c>
       <c r="C231" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="D231" t="n">
         <v>0.64</v>
-      </c>
-      <c r="D231" t="n">
-        <v>0.57</v>
       </c>
       <c r="E231" t="n">
         <v>0.36</v>
       </c>
       <c r="F231" t="n">
-        <v>0.5625</v>
+        <v>0.6315789473684211</v>
       </c>
       <c r="G231" t="n">
         <v>0.986842105263158</v>
@@ -11579,16 +11579,16 @@
         <v>-0.004799999999999971</v>
       </c>
       <c r="J231" t="n">
-        <v>0.982857142857143</v>
+        <v>0.9771428571428573</v>
       </c>
       <c r="K231" t="n">
-        <v>-0.0357142857142855</v>
+        <v>-0.03007518796992463</v>
       </c>
       <c r="L231" t="n">
         <v>0.4235294117647059</v>
       </c>
       <c r="M231" t="n">
-        <v>-0.01744186046511616</v>
+        <v>-0.0233918128654969</v>
       </c>
       <c r="N231" t="n">
         <v>0.5970394736842106</v>
@@ -12173,7 +12173,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Game Edukasi', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12221,7 +12221,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan', 'Data mining'})</t>
+          <t>frozenset({'Data mining', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12269,7 +12269,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Data mining'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12317,7 +12317,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12326,13 +12326,13 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="D247" t="n">
         <v>0.68</v>
       </c>
       <c r="E247" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="F247" t="n">
         <v>0.6666666666666667</v>
@@ -12344,28 +12344,28 @@
         <v>1</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.002799999999999997</v>
+        <v>-0.003200000000000008</v>
       </c>
       <c r="J247" t="n">
         <v>0.9600000000000001</v>
       </c>
       <c r="K247" t="n">
-        <v>-0.02469135802469133</v>
+        <v>-0.02564102564102571</v>
       </c>
       <c r="L247" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="M247" t="n">
         <v>-0.04166666666666659</v>
       </c>
       <c r="N247" t="n">
-        <v>0.4362745098039216</v>
+        <v>0.4509803921568628</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -12374,13 +12374,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="D248" t="n">
         <v>0.68</v>
       </c>
       <c r="E248" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="F248" t="n">
         <v>0.6666666666666667</v>
@@ -12392,28 +12392,28 @@
         <v>1</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.003200000000000008</v>
+        <v>-0.002799999999999997</v>
       </c>
       <c r="J248" t="n">
         <v>0.9600000000000001</v>
       </c>
       <c r="K248" t="n">
-        <v>-0.02564102564102571</v>
+        <v>-0.02469135802469133</v>
       </c>
       <c r="L248" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1866666666666667</v>
       </c>
       <c r="M248" t="n">
         <v>-0.04166666666666659</v>
       </c>
       <c r="N248" t="n">
-        <v>0.4509803921568628</v>
+        <v>0.4362745098039216</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -12461,7 +12461,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -12509,7 +12509,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Teknologi IoT', 'Data mining'})</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -12557,7 +12557,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -12566,13 +12566,13 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="D252" t="n">
         <v>0.68</v>
       </c>
       <c r="E252" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="F252" t="n">
         <v>0.6666666666666666</v>
@@ -12584,22 +12584,22 @@
         <v>1</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.002400000000000013</v>
+        <v>-0.004400000000000015</v>
       </c>
       <c r="J252" t="n">
         <v>0.9599999999999997</v>
       </c>
       <c r="K252" t="n">
-        <v>-0.02380952380952394</v>
+        <v>-0.02898550724637691</v>
       </c>
       <c r="L252" t="n">
-        <v>0.1621621621621621</v>
+        <v>0.2784810126582278</v>
       </c>
       <c r="M252" t="n">
         <v>-0.04166666666666694</v>
       </c>
       <c r="N252" t="n">
-        <v>0.4215686274509803</v>
+        <v>0.4950980392156862</v>
       </c>
     </row>
     <row r="253">
@@ -12653,7 +12653,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -12662,13 +12662,13 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>0.33</v>
+        <v>0.18</v>
       </c>
       <c r="D254" t="n">
         <v>0.68</v>
       </c>
       <c r="E254" t="n">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="F254" t="n">
         <v>0.6666666666666666</v>
@@ -12680,22 +12680,22 @@
         <v>1</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.004400000000000015</v>
+        <v>-0.002400000000000013</v>
       </c>
       <c r="J254" t="n">
         <v>0.9599999999999997</v>
       </c>
       <c r="K254" t="n">
-        <v>-0.02898550724637691</v>
+        <v>-0.02380952380952394</v>
       </c>
       <c r="L254" t="n">
-        <v>0.2784810126582278</v>
+        <v>0.1621621621621621</v>
       </c>
       <c r="M254" t="n">
         <v>-0.04166666666666694</v>
       </c>
       <c r="N254" t="n">
-        <v>0.4950980392156862</v>
+        <v>0.4215686274509803</v>
       </c>
     </row>
     <row r="255">
@@ -12749,7 +12749,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -12941,7 +12941,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13037,7 +13037,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining'})</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13085,7 +13085,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -13181,25 +13181,25 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
+          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
           <t>frozenset({'Data mining'})</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
-        </is>
-      </c>
       <c r="C265" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D265" t="n">
         <v>0.64</v>
-      </c>
-      <c r="D265" t="n">
-        <v>0.53</v>
       </c>
       <c r="E265" t="n">
         <v>0.33</v>
       </c>
       <c r="F265" t="n">
-        <v>0.515625</v>
+        <v>0.6226415094339622</v>
       </c>
       <c r="G265" t="n">
         <v>0.972877358490566</v>
@@ -13211,16 +13211,16 @@
         <v>-0.009199999999999986</v>
       </c>
       <c r="J265" t="n">
-        <v>0.9703225806451612</v>
+        <v>0.9539999999999998</v>
       </c>
       <c r="K265" t="n">
-        <v>-0.07187499999999988</v>
+        <v>-0.05599513085818616</v>
       </c>
       <c r="L265" t="n">
         <v>0.392857142857143</v>
       </c>
       <c r="M265" t="n">
-        <v>-0.03058510638297878</v>
+        <v>-0.04821802935010493</v>
       </c>
       <c r="N265" t="n">
         <v>0.5691332547169812</v>
@@ -13229,25 +13229,25 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
+          <t>frozenset({'Data mining'})</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
           <t>frozenset({'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>frozenset({'Data mining'})</t>
-        </is>
-      </c>
       <c r="C266" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D266" t="n">
         <v>0.53</v>
-      </c>
-      <c r="D266" t="n">
-        <v>0.64</v>
       </c>
       <c r="E266" t="n">
         <v>0.33</v>
       </c>
       <c r="F266" t="n">
-        <v>0.6226415094339622</v>
+        <v>0.515625</v>
       </c>
       <c r="G266" t="n">
         <v>0.972877358490566</v>
@@ -13259,16 +13259,16 @@
         <v>-0.009199999999999986</v>
       </c>
       <c r="J266" t="n">
-        <v>0.9539999999999998</v>
+        <v>0.9703225806451612</v>
       </c>
       <c r="K266" t="n">
-        <v>-0.05599513085818616</v>
+        <v>-0.07187499999999988</v>
       </c>
       <c r="L266" t="n">
         <v>0.392857142857143</v>
       </c>
       <c r="M266" t="n">
-        <v>-0.04821802935010493</v>
+        <v>-0.03058510638297878</v>
       </c>
       <c r="N266" t="n">
         <v>0.5691332547169812</v>
@@ -13277,25 +13277,25 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Game Edukasi', 'Pemrograman CMS'})</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
           <t>frozenset({'Realitas Virtual'})</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
-        </is>
-      </c>
       <c r="C267" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D267" t="n">
         <v>0.87</v>
       </c>
-      <c r="D267" t="n">
-        <v>0.65</v>
-      </c>
       <c r="E267" t="n">
-        <v>0.55</v>
+        <v>0.11</v>
       </c>
       <c r="F267" t="n">
-        <v>0.632183908045977</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="G267" t="n">
         <v>0.9725906277630415</v>
@@ -13304,28 +13304,28 @@
         <v>1</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.01549999999999996</v>
+        <v>-0.003100000000000006</v>
       </c>
       <c r="J267" t="n">
-        <v>0.9515625</v>
+        <v>0.845</v>
       </c>
       <c r="K267" t="n">
-        <v>-0.1781609195402294</v>
+        <v>-0.03137651821862354</v>
       </c>
       <c r="L267" t="n">
-        <v>0.5670103092783506</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="M267" t="n">
-        <v>-0.05090311986863716</v>
+        <v>-0.1834319526627219</v>
       </c>
       <c r="N267" t="n">
-        <v>0.7391688770999116</v>
+        <v>0.4862953138815208</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -13334,13 +13334,13 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>0.13</v>
+        <v>0.65</v>
       </c>
       <c r="D268" t="n">
         <v>0.87</v>
       </c>
       <c r="E268" t="n">
-        <v>0.11</v>
+        <v>0.55</v>
       </c>
       <c r="F268" t="n">
         <v>0.8461538461538461</v>
@@ -13352,46 +13352,46 @@
         <v>1</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.003100000000000006</v>
+        <v>-0.01549999999999996</v>
       </c>
       <c r="J268" t="n">
         <v>0.845</v>
       </c>
       <c r="K268" t="n">
-        <v>-0.03137651821862354</v>
+        <v>-0.07451923076923059</v>
       </c>
       <c r="L268" t="n">
-        <v>0.1235955056179775</v>
+        <v>0.5670103092783506</v>
       </c>
       <c r="M268" t="n">
         <v>-0.1834319526627219</v>
       </c>
       <c r="N268" t="n">
-        <v>0.4862953138815208</v>
+        <v>0.7391688770999116</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
+          <t>frozenset({'Realitas Virtual'})</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
           <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>frozenset({'Realitas Virtual'})</t>
-        </is>
-      </c>
       <c r="C269" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="D269" t="n">
         <v>0.65</v>
-      </c>
-      <c r="D269" t="n">
-        <v>0.87</v>
       </c>
       <c r="E269" t="n">
         <v>0.55</v>
       </c>
       <c r="F269" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.632183908045977</v>
       </c>
       <c r="G269" t="n">
         <v>0.9725906277630415</v>
@@ -13403,16 +13403,16 @@
         <v>-0.01549999999999996</v>
       </c>
       <c r="J269" t="n">
-        <v>0.845</v>
+        <v>0.9515625</v>
       </c>
       <c r="K269" t="n">
-        <v>-0.07451923076923059</v>
+        <v>-0.1781609195402294</v>
       </c>
       <c r="L269" t="n">
         <v>0.5670103092783506</v>
       </c>
       <c r="M269" t="n">
-        <v>-0.1834319526627219</v>
+        <v>-0.05090311986863716</v>
       </c>
       <c r="N269" t="n">
         <v>0.7391688770999116</v>
@@ -13421,7 +13421,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13661,7 +13661,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13709,12 +13709,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -13805,25 +13805,25 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
+          <t>frozenset({'Realitas Virtual'})</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
           <t>frozenset({'Pengolahan Citra Digital'})</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>frozenset({'Realitas Virtual'})</t>
-        </is>
-      </c>
       <c r="C278" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="D278" t="n">
         <v>0.68</v>
-      </c>
-      <c r="D278" t="n">
-        <v>0.87</v>
       </c>
       <c r="E278" t="n">
         <v>0.57</v>
       </c>
       <c r="F278" t="n">
-        <v>0.838235294117647</v>
+        <v>0.6551724137931034</v>
       </c>
       <c r="G278" t="n">
         <v>0.9634888438133873</v>
@@ -13835,16 +13835,16 @@
         <v>-0.02160000000000006</v>
       </c>
       <c r="J278" t="n">
-        <v>0.8036363636363633</v>
+        <v>0.9279999999999998</v>
       </c>
       <c r="K278" t="n">
-        <v>-0.1058823529411768</v>
+        <v>-0.2257053291536055</v>
       </c>
       <c r="L278" t="n">
         <v>0.5816326530612244</v>
       </c>
       <c r="M278" t="n">
-        <v>-0.2443438914027156</v>
+        <v>-0.07758620689655196</v>
       </c>
       <c r="N278" t="n">
         <v>0.7467038539553752</v>
@@ -13853,25 +13853,25 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
+          <t>frozenset({'Pengolahan Citra Digital'})</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
           <t>frozenset({'Realitas Virtual'})</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>frozenset({'Pengolahan Citra Digital'})</t>
-        </is>
-      </c>
       <c r="C279" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D279" t="n">
         <v>0.87</v>
-      </c>
-      <c r="D279" t="n">
-        <v>0.68</v>
       </c>
       <c r="E279" t="n">
         <v>0.57</v>
       </c>
       <c r="F279" t="n">
-        <v>0.6551724137931034</v>
+        <v>0.838235294117647</v>
       </c>
       <c r="G279" t="n">
         <v>0.9634888438133873</v>
@@ -13883,16 +13883,16 @@
         <v>-0.02160000000000006</v>
       </c>
       <c r="J279" t="n">
-        <v>0.9279999999999998</v>
+        <v>0.8036363636363633</v>
       </c>
       <c r="K279" t="n">
-        <v>-0.2257053291536055</v>
+        <v>-0.1058823529411768</v>
       </c>
       <c r="L279" t="n">
         <v>0.5816326530612244</v>
       </c>
       <c r="M279" t="n">
-        <v>-0.07758620689655196</v>
+        <v>-0.2443438914027156</v>
       </c>
       <c r="N279" t="n">
         <v>0.7467038539553752</v>
@@ -13901,7 +13901,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining'})</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13949,25 +13949,25 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
+          <t>frozenset({'Pengolahan Citra Digital'})</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
           <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>frozenset({'Pengolahan Citra Digital'})</t>
-        </is>
-      </c>
       <c r="C281" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D281" t="n">
         <v>0.55</v>
-      </c>
-      <c r="D281" t="n">
-        <v>0.68</v>
       </c>
       <c r="E281" t="n">
         <v>0.36</v>
       </c>
       <c r="F281" t="n">
-        <v>0.6545454545454544</v>
+        <v>0.5294117647058822</v>
       </c>
       <c r="G281" t="n">
         <v>0.9625668449197858</v>
@@ -13979,16 +13979,16 @@
         <v>-0.01400000000000007</v>
       </c>
       <c r="J281" t="n">
-        <v>0.9263157894736838</v>
+        <v>0.9562499999999997</v>
       </c>
       <c r="K281" t="n">
-        <v>-0.07954545454545491</v>
+        <v>-0.1083591331269355</v>
       </c>
       <c r="L281" t="n">
         <v>0.4137931034482759</v>
       </c>
       <c r="M281" t="n">
-        <v>-0.07954545454545507</v>
+        <v>-0.04575163398692844</v>
       </c>
       <c r="N281" t="n">
         <v>0.5919786096256683</v>
@@ -13997,25 +13997,25 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
+          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
           <t>frozenset({'Pengolahan Citra Digital'})</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining'})</t>
-        </is>
-      </c>
       <c r="C282" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D282" t="n">
         <v>0.68</v>
-      </c>
-      <c r="D282" t="n">
-        <v>0.55</v>
       </c>
       <c r="E282" t="n">
         <v>0.36</v>
       </c>
       <c r="F282" t="n">
-        <v>0.5294117647058822</v>
+        <v>0.6545454545454544</v>
       </c>
       <c r="G282" t="n">
         <v>0.9625668449197858</v>
@@ -14027,16 +14027,16 @@
         <v>-0.01400000000000007</v>
       </c>
       <c r="J282" t="n">
-        <v>0.9562499999999997</v>
+        <v>0.9263157894736838</v>
       </c>
       <c r="K282" t="n">
-        <v>-0.1083591331269355</v>
+        <v>-0.07954545454545491</v>
       </c>
       <c r="L282" t="n">
         <v>0.4137931034482759</v>
       </c>
       <c r="M282" t="n">
-        <v>-0.04575163398692844</v>
+        <v>-0.07954545454545507</v>
       </c>
       <c r="N282" t="n">
         <v>0.5919786096256683</v>
@@ -14045,7 +14045,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -14093,7 +14093,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -14194,7 +14194,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -14237,7 +14237,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -14246,13 +14246,13 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D287" t="n">
         <v>0.68</v>
       </c>
       <c r="E287" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="F287" t="n">
         <v>0.65</v>
@@ -14264,28 +14264,28 @@
         <v>1</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.01200000000000001</v>
+        <v>-0.006000000000000005</v>
       </c>
       <c r="J287" t="n">
         <v>0.9142857142857143</v>
       </c>
       <c r="K287" t="n">
-        <v>-0.07142857142857148</v>
+        <v>-0.05454545454545458</v>
       </c>
       <c r="L287" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.1733333333333333</v>
       </c>
       <c r="M287" t="n">
         <v>-0.0937500000000001</v>
       </c>
       <c r="N287" t="n">
-        <v>0.5161764705882352</v>
+        <v>0.4205882352941177</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -14333,7 +14333,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Data mining', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -14342,13 +14342,13 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D289" t="n">
         <v>0.68</v>
       </c>
       <c r="E289" t="n">
-        <v>0.13</v>
+        <v>0.26</v>
       </c>
       <c r="F289" t="n">
         <v>0.65</v>
@@ -14360,28 +14360,28 @@
         <v>1</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.006000000000000005</v>
+        <v>-0.01200000000000001</v>
       </c>
       <c r="J289" t="n">
         <v>0.9142857142857143</v>
       </c>
       <c r="K289" t="n">
-        <v>-0.05454545454545458</v>
+        <v>-0.07142857142857148</v>
       </c>
       <c r="L289" t="n">
-        <v>0.1733333333333333</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="M289" t="n">
         <v>-0.0937500000000001</v>
       </c>
       <c r="N289" t="n">
-        <v>0.4205882352941177</v>
+        <v>0.5161764705882352</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -14525,7 +14525,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -14573,7 +14573,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -14621,7 +14621,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -14669,7 +14669,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Game Edukasi'})</t>
+          <t>frozenset({'Data mining', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -14717,7 +14717,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -14765,7 +14765,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -14861,7 +14861,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Game Edukasi'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -14957,7 +14957,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -15005,7 +15005,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -15053,7 +15053,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -15101,7 +15101,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -15149,7 +15149,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining'})</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -15197,7 +15197,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -15293,7 +15293,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -15341,7 +15341,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -15437,7 +15437,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>frozenset({'Pengolahan Citra Digital', 'Game Edukasi'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -15446,13 +15446,13 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>0.38</v>
+        <v>0.24</v>
       </c>
       <c r="D312" t="n">
         <v>0.54</v>
       </c>
       <c r="E312" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="F312" t="n">
         <v>0.5</v>
@@ -15464,28 +15464,28 @@
         <v>1</v>
       </c>
       <c r="I312" t="n">
-        <v>-0.01520000000000002</v>
+        <v>-0.009599999999999997</v>
       </c>
       <c r="J312" t="n">
         <v>0.9199999999999999</v>
       </c>
       <c r="K312" t="n">
-        <v>-0.1142857142857144</v>
+        <v>-0.09523809523809521</v>
       </c>
       <c r="L312" t="n">
-        <v>0.2602739726027397</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="M312" t="n">
         <v>-0.08695652173913052</v>
       </c>
       <c r="N312" t="n">
-        <v>0.4259259259259259</v>
+        <v>0.3611111111111111</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -15494,13 +15494,13 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>0.24</v>
+        <v>0.38</v>
       </c>
       <c r="D313" t="n">
         <v>0.54</v>
       </c>
       <c r="E313" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="F313" t="n">
         <v>0.5</v>
@@ -15512,28 +15512,28 @@
         <v>1</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.009599999999999997</v>
+        <v>-0.01520000000000002</v>
       </c>
       <c r="J313" t="n">
         <v>0.9199999999999999</v>
       </c>
       <c r="K313" t="n">
-        <v>-0.09523809523809521</v>
+        <v>-0.1142857142857144</v>
       </c>
       <c r="L313" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.2602739726027397</v>
       </c>
       <c r="M313" t="n">
         <v>-0.08695652173913052</v>
       </c>
       <c r="N313" t="n">
-        <v>0.3611111111111111</v>
+        <v>0.4259259259259259</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -15581,7 +15581,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining'})</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -15725,7 +15725,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis'})</t>
+          <t>frozenset({'Data mining', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -15734,13 +15734,13 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>0.32</v>
+        <v>0.16</v>
       </c>
       <c r="D318" t="n">
         <v>0.82</v>
       </c>
       <c r="E318" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="F318" t="n">
         <v>0.75</v>
@@ -15752,28 +15752,28 @@
         <v>1</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.02239999999999998</v>
+        <v>-0.01119999999999999</v>
       </c>
       <c r="J318" t="n">
         <v>0.7200000000000002</v>
       </c>
       <c r="K318" t="n">
-        <v>-0.1206896551724137</v>
+        <v>-0.09999999999999989</v>
       </c>
       <c r="L318" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.1395348837209302</v>
       </c>
       <c r="M318" t="n">
         <v>-0.3888888888888885</v>
       </c>
       <c r="N318" t="n">
-        <v>0.5213414634146342</v>
+        <v>0.4481707317073171</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Game Edukasi'})</t>
+          <t>frozenset({'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -15782,13 +15782,13 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="D319" t="n">
         <v>0.82</v>
       </c>
       <c r="E319" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="F319" t="n">
         <v>0.75</v>
@@ -15800,28 +15800,28 @@
         <v>1</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.01679999999999998</v>
+        <v>-0.02239999999999998</v>
       </c>
       <c r="J319" t="n">
         <v>0.7200000000000002</v>
       </c>
       <c r="K319" t="n">
-        <v>-0.1093749999999999</v>
+        <v>-0.1206896551724137</v>
       </c>
       <c r="L319" t="n">
-        <v>0.2045454545454545</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="M319" t="n">
         <v>-0.3888888888888885</v>
       </c>
       <c r="N319" t="n">
-        <v>0.4847560975609756</v>
+        <v>0.5213414634146342</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining'})</t>
+          <t>frozenset({'Game Edukasi', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="D320" t="n">
         <v>0.82</v>
       </c>
       <c r="E320" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="F320" t="n">
         <v>0.75</v>
@@ -15848,22 +15848,22 @@
         <v>1</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.01119999999999999</v>
+        <v>-0.01679999999999998</v>
       </c>
       <c r="J320" t="n">
         <v>0.7200000000000002</v>
       </c>
       <c r="K320" t="n">
-        <v>-0.09999999999999989</v>
+        <v>-0.1093749999999999</v>
       </c>
       <c r="L320" t="n">
-        <v>0.1395348837209302</v>
+        <v>0.2045454545454545</v>
       </c>
       <c r="M320" t="n">
         <v>-0.3888888888888885</v>
       </c>
       <c r="N320" t="n">
-        <v>0.4481707317073171</v>
+        <v>0.4847560975609756</v>
       </c>
     </row>
     <row r="321">
@@ -15917,7 +15917,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Game Edukasi'})</t>
+          <t>frozenset({'Game Edukasi', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -16061,25 +16061,25 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
+          <t>frozenset({'Game Edukasi', 'Pemrograman CMS'})</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
           <t>frozenset({'Pengolahan Citra Digital'})</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>frozenset({'Game Edukasi', 'Pemrograman CMS'})</t>
-        </is>
-      </c>
       <c r="C325" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D325" t="n">
         <v>0.68</v>
-      </c>
-      <c r="D325" t="n">
-        <v>0.6</v>
       </c>
       <c r="E325" t="n">
         <v>0.37</v>
       </c>
       <c r="F325" t="n">
-        <v>0.5441176470588235</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="G325" t="n">
         <v>0.9068627450980392</v>
@@ -16091,16 +16091,16 @@
         <v>-0.03800000000000003</v>
       </c>
       <c r="J325" t="n">
-        <v>0.8774193548387096</v>
+        <v>0.8347826086956521</v>
       </c>
       <c r="K325" t="n">
-        <v>-0.2429667519181588</v>
+        <v>-0.2043010752688174</v>
       </c>
       <c r="L325" t="n">
         <v>0.4065934065934066</v>
       </c>
       <c r="M325" t="n">
-        <v>-0.1397058823529412</v>
+        <v>-0.1979166666666668</v>
       </c>
       <c r="N325" t="n">
         <v>0.580392156862745</v>
@@ -16109,25 +16109,25 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
+          <t>frozenset({'Pengolahan Citra Digital'})</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
           <t>frozenset({'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>frozenset({'Pengolahan Citra Digital'})</t>
-        </is>
-      </c>
       <c r="C326" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D326" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D326" t="n">
-        <v>0.68</v>
       </c>
       <c r="E326" t="n">
         <v>0.37</v>
       </c>
       <c r="F326" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.5441176470588235</v>
       </c>
       <c r="G326" t="n">
         <v>0.9068627450980392</v>
@@ -16139,16 +16139,16 @@
         <v>-0.03800000000000003</v>
       </c>
       <c r="J326" t="n">
-        <v>0.8347826086956521</v>
+        <v>0.8774193548387096</v>
       </c>
       <c r="K326" t="n">
-        <v>-0.2043010752688174</v>
+        <v>-0.2429667519181588</v>
       </c>
       <c r="L326" t="n">
         <v>0.4065934065934066</v>
       </c>
       <c r="M326" t="n">
-        <v>-0.1979166666666668</v>
+        <v>-0.1397058823529412</v>
       </c>
       <c r="N326" t="n">
         <v>0.580392156862745</v>
@@ -16301,7 +16301,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -16349,7 +16349,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Desain Grafis', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -16397,7 +16397,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Desain Grafis', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Game Edukasi', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -16493,7 +16493,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -16541,7 +16541,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -16637,7 +16637,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -16685,7 +16685,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -16781,7 +16781,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -16829,7 +16829,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Desain Grafis', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Game Edukasi', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -16877,7 +16877,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -16886,13 +16886,13 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="D342" t="n">
         <v>0.62</v>
       </c>
       <c r="E342" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="F342" t="n">
         <v>0.5454545454545454</v>
@@ -16904,28 +16904,28 @@
         <v>1</v>
       </c>
       <c r="I342" t="n">
-        <v>-0.02460000000000001</v>
+        <v>-0.0164</v>
       </c>
       <c r="J342" t="n">
         <v>0.836</v>
       </c>
       <c r="K342" t="n">
-        <v>-0.1694214876033059</v>
+        <v>-0.1490909090909091</v>
       </c>
       <c r="L342" t="n">
-        <v>0.2337662337662338</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M342" t="n">
         <v>-0.1961722488038278</v>
       </c>
       <c r="N342" t="n">
-        <v>0.4178885630498533</v>
+        <v>0.3695014662756598</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -16934,13 +16934,13 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="D343" t="n">
         <v>0.62</v>
       </c>
       <c r="E343" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="F343" t="n">
         <v>0.5454545454545454</v>
@@ -16952,28 +16952,28 @@
         <v>1</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.0164</v>
+        <v>-0.02460000000000001</v>
       </c>
       <c r="J343" t="n">
         <v>0.836</v>
       </c>
       <c r="K343" t="n">
-        <v>-0.1490909090909091</v>
+        <v>-0.1694214876033059</v>
       </c>
       <c r="L343" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2337662337662338</v>
       </c>
       <c r="M343" t="n">
         <v>-0.1961722488038278</v>
       </c>
       <c r="N343" t="n">
-        <v>0.3695014662756598</v>
+        <v>0.4178885630498533</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -17117,7 +17117,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -17165,7 +17165,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Data mining', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -17213,7 +17213,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Data mining'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Data mining', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -17261,7 +17261,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Game Edukasi'})</t>
+          <t>frozenset({'Game Edukasi', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -17309,7 +17309,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Teknologi IoT'})</t>
+          <t>frozenset({'Teknologi IoT', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -17357,7 +17357,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Data mining'})</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -17405,7 +17405,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -17453,7 +17453,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -17501,7 +17501,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -17549,7 +17549,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -17645,7 +17645,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Realitas Virtual', 'Data mining', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Realitas Virtual', 'Data mining', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -17693,7 +17693,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Game Edukasi', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -17789,7 +17789,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Game Edukasi'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -17885,7 +17885,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>frozenset({'Data mining', 'Pengolahan Citra Digital', 'Game Edukasi'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining', 'Game Edukasi', 'Pemrograman CMS'})</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -17933,7 +17933,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Data mining', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Data mining', 'Game Edukasi'})</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -18029,7 +18029,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Pengolahan Citra Digital', 'Teknologi IoT'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Teknologi IoT', 'Realitas Virtual'})</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -18125,7 +18125,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -18221,7 +18221,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -18269,7 +18269,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Game Edukasi'})</t>
+          <t>frozenset({'Game Edukasi', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -18317,7 +18317,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis'})</t>
+          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -18326,13 +18326,13 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="D372" t="n">
         <v>0.63</v>
       </c>
       <c r="E372" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="F372" t="n">
         <v>0.5</v>
@@ -18344,28 +18344,28 @@
         <v>1</v>
       </c>
       <c r="I372" t="n">
-        <v>-0.0416</v>
+        <v>-0.03120000000000001</v>
       </c>
       <c r="J372" t="n">
         <v>0.74</v>
       </c>
       <c r="K372" t="n">
-        <v>-0.276595744680851</v>
+        <v>-0.2549019607843138</v>
       </c>
       <c r="L372" t="n">
-        <v>0.2025316455696203</v>
+        <v>0.16</v>
       </c>
       <c r="M372" t="n">
         <v>-0.3513513513513514</v>
       </c>
       <c r="N372" t="n">
-        <v>0.376984126984127</v>
+        <v>0.3452380952380952</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -18374,13 +18374,13 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="D373" t="n">
         <v>0.63</v>
       </c>
       <c r="E373" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="F373" t="n">
         <v>0.5</v>
@@ -18392,28 +18392,28 @@
         <v>1</v>
       </c>
       <c r="I373" t="n">
-        <v>-0.03120000000000001</v>
+        <v>-0.0416</v>
       </c>
       <c r="J373" t="n">
         <v>0.74</v>
       </c>
       <c r="K373" t="n">
-        <v>-0.2549019607843138</v>
+        <v>-0.276595744680851</v>
       </c>
       <c r="L373" t="n">
-        <v>0.16</v>
+        <v>0.2025316455696203</v>
       </c>
       <c r="M373" t="n">
         <v>-0.3513513513513514</v>
       </c>
       <c r="N373" t="n">
-        <v>0.3452380952380952</v>
+        <v>0.376984126984127</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Sistem Keamanan Jaringan'})</t>
+          <t>frozenset({'Sistem Keamanan Jaringan'})</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -18461,7 +18461,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pengolahan Citra Digital', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Pemrograman CMS', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -18509,7 +18509,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis'})</t>
+          <t>frozenset({'Realitas Virtual', 'Pemrograman CMS', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -18518,13 +18518,13 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="D376" t="n">
         <v>0.64</v>
       </c>
       <c r="E376" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="F376" t="n">
         <v>0.5</v>
@@ -18536,28 +18536,28 @@
         <v>1</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.04480000000000001</v>
+        <v>-0.03359999999999999</v>
       </c>
       <c r="J376" t="n">
         <v>0.72</v>
       </c>
       <c r="K376" t="n">
-        <v>-0.2916666666666667</v>
+        <v>-0.2692307692307692</v>
       </c>
       <c r="L376" t="n">
-        <v>0.2</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="M376" t="n">
         <v>-0.388888888888889</v>
       </c>
       <c r="N376" t="n">
-        <v>0.375</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>frozenset({'Realitas Virtual', 'Desain Grafis', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -18566,13 +18566,13 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="D377" t="n">
         <v>0.64</v>
       </c>
       <c r="E377" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="F377" t="n">
         <v>0.5</v>
@@ -18584,28 +18584,28 @@
         <v>1</v>
       </c>
       <c r="I377" t="n">
-        <v>-0.03359999999999999</v>
+        <v>-0.04480000000000001</v>
       </c>
       <c r="J377" t="n">
         <v>0.72</v>
       </c>
       <c r="K377" t="n">
-        <v>-0.2692307692307692</v>
+        <v>-0.2916666666666667</v>
       </c>
       <c r="L377" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.2</v>
       </c>
       <c r="M377" t="n">
         <v>-0.388888888888889</v>
       </c>
       <c r="N377" t="n">
-        <v>0.34375</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis'})</t>
+          <t>frozenset({'Game Edukasi', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -18614,13 +18614,13 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="D378" t="n">
         <v>0.65</v>
       </c>
       <c r="E378" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="F378" t="n">
         <v>0.5</v>
@@ -18632,28 +18632,28 @@
         <v>1</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.04800000000000001</v>
+        <v>-0.036</v>
       </c>
       <c r="J378" t="n">
         <v>0.7</v>
       </c>
       <c r="K378" t="n">
-        <v>-0.306122448979592</v>
+        <v>-0.2830188679245283</v>
       </c>
       <c r="L378" t="n">
-        <v>0.1975308641975309</v>
+        <v>0.1558441558441558</v>
       </c>
       <c r="M378" t="n">
         <v>-0.4285714285714287</v>
       </c>
       <c r="N378" t="n">
-        <v>0.3730769230769231</v>
+        <v>0.3423076923076923</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Game Edukasi'})</t>
+          <t>frozenset({'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -18662,13 +18662,13 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="D379" t="n">
         <v>0.65</v>
       </c>
       <c r="E379" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="F379" t="n">
         <v>0.5</v>
@@ -18680,28 +18680,28 @@
         <v>1</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.036</v>
+        <v>-0.04800000000000001</v>
       </c>
       <c r="J379" t="n">
         <v>0.7</v>
       </c>
       <c r="K379" t="n">
-        <v>-0.2830188679245283</v>
+        <v>-0.306122448979592</v>
       </c>
       <c r="L379" t="n">
-        <v>0.1558441558441558</v>
+        <v>0.1975308641975309</v>
       </c>
       <c r="M379" t="n">
         <v>-0.4285714285714287</v>
       </c>
       <c r="N379" t="n">
-        <v>0.3423076923076923</v>
+        <v>0.3730769230769231</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>frozenset({'Game Edukasi', 'Desain Grafis', 'Pemrograman CMS'})</t>
+          <t>frozenset({'Pemrograman CMS', 'Game Edukasi', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -18749,7 +18749,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>frozenset({'Desain Grafis', 'Pengolahan Citra Digital'})</t>
+          <t>frozenset({'Pengolahan Citra Digital', 'Desain Grafis'})</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
